--- a/projects/KE_Kapiti_Eddy_July/KE_Kapiti_output_eddy/Kapiti.Biomass.Clippings.xlsx
+++ b/projects/KE_Kapiti_Eddy_July/KE_Kapiti_output_eddy/Kapiti.Biomass.Clippings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\Soil.C.modelling\Kapiti.soil.C\projects\KE_Kapiti_Eddy_July\KE_Kapiti_output_eddy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\L-DNDC\Landscape-DNDC\projects\KE_Kapiti_Eddy_July\KE_Kapiti_output_eddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5294D45E-B23C-439C-8CD1-EADEBA00AE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{F9685192-7F5D-44C7-BE52-AE5DC9386920}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{F9685192-7F5D-44C7-BE52-AE5DC9386920}"/>
   </bookViews>
   <sheets>
     <sheet name="KAPITI_BIOMASS_CAGES_RAW_REVD" sheetId="6" r:id="rId1"/>
@@ -3381,22 +3381,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA41F3B-99A8-4179-B107-E811EB6FB535}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:W445"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.83984375" customWidth="1"/>
+    <col min="2" max="2" width="17.26171875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="6" max="8" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.26171875" customWidth="1"/>
+    <col min="6" max="8" width="27.26171875" customWidth="1"/>
     <col min="9" max="10" width="18" customWidth="1"/>
-    <col min="11" max="18" width="16.85546875" customWidth="1"/>
-    <col min="19" max="19" width="26.85546875" customWidth="1"/>
-    <col min="20" max="20" width="17.140625" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" customWidth="1"/>
+    <col min="11" max="18" width="16.83984375" customWidth="1"/>
+    <col min="19" max="19" width="26.83984375" customWidth="1"/>
+    <col min="20" max="20" width="17.15625" customWidth="1"/>
+    <col min="21" max="21" width="20.83984375" customWidth="1"/>
+    <col min="22" max="22" width="15.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15">
         <v>44599</v>
       </c>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="W2" s="1"/>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15">
         <v>44599</v>
       </c>
@@ -3568,7 +3568,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1">
-        <f t="shared" ref="N3:N66" si="2">IF(H3=0,0.9,0.27)</f>
+        <f t="shared" ref="N3:N4" si="2">IF(H3=0,0.9,0.27)</f>
         <v>0.9</v>
       </c>
       <c r="O3" s="1"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="15">
         <v>44600</v>
       </c>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W4" s="1"/>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15">
         <v>44600</v>
       </c>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="W5" s="1"/>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="15">
         <v>44609</v>
       </c>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="W6" s="1"/>
     </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15">
         <v>44609</v>
       </c>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="W7" s="1"/>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15">
         <v>44609</v>
       </c>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="W8" s="1"/>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="15">
         <v>44609</v>
       </c>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="W9" s="1"/>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15">
         <v>44610</v>
       </c>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="15">
         <v>44610</v>
       </c>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="W11" s="1"/>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="15">
         <v>44610</v>
       </c>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="W12" s="1"/>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="15">
         <v>44610</v>
       </c>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="W13" s="1"/>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="15">
         <v>44610</v>
       </c>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="15">
         <v>44610</v>
       </c>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="15">
         <v>44613</v>
       </c>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="W16" s="1"/>
     </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="15">
         <v>44613</v>
       </c>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="W17" s="1"/>
     </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="15">
         <v>44615</v>
       </c>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="15">
         <v>44615</v>
       </c>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="15">
         <v>44615</v>
       </c>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="15">
         <v>44615</v>
       </c>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="15">
         <v>44616</v>
       </c>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="W22" s="1"/>
     </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="15">
         <v>44616</v>
       </c>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="15">
         <v>44616</v>
       </c>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="W24" s="1"/>
     </row>
-    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="15">
         <v>44616</v>
       </c>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="W25" s="1"/>
     </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="15">
         <v>44622</v>
       </c>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="15">
         <v>44622</v>
       </c>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="15">
         <v>44622</v>
       </c>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="15">
         <v>44622</v>
       </c>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W29" s="1"/>
     </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="15">
         <v>44622</v>
       </c>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="W30" s="1"/>
     </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="15">
         <v>44622</v>
       </c>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="W31" s="1"/>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="15">
         <v>44622</v>
       </c>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="W32" s="1"/>
     </row>
-    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="15">
         <v>44622</v>
       </c>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="W33" s="1"/>
     </row>
-    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="15">
         <v>44622</v>
       </c>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="W34" s="1"/>
     </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="15">
         <v>44622</v>
       </c>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="W35" s="1"/>
     </row>
-    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="15">
         <v>44622</v>
       </c>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W36" s="1"/>
     </row>
-    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="15">
         <v>44622</v>
       </c>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="W37" s="1"/>
     </row>
-    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="15">
         <v>44622</v>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="W38" s="1"/>
     </row>
-    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="15">
         <v>44622</v>
       </c>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="15">
         <v>44622</v>
       </c>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="15">
         <v>44622</v>
       </c>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="15">
         <v>44599</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="15">
         <v>44629</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="15">
         <v>44629</v>
       </c>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="W44" s="1"/>
     </row>
-    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="15">
         <v>44629</v>
       </c>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="W45" s="1"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="15">
         <v>44629</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="15">
         <v>44629</v>
       </c>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="W47" s="1"/>
     </row>
-    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="15">
         <v>44630</v>
       </c>
@@ -6415,7 +6415,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="15">
         <v>44630</v>
       </c>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="W49" s="1"/>
     </row>
-    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="15">
         <v>44873</v>
       </c>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W50" s="1"/>
     </row>
-    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="15">
         <v>44873</v>
       </c>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="W51" s="1"/>
     </row>
-    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="15">
         <v>44873</v>
       </c>
@@ -6644,7 +6644,7 @@
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="15">
         <v>44873</v>
       </c>
@@ -6687,7 +6687,7 @@
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
     </row>
-    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="15">
         <v>44873</v>
       </c>
@@ -6732,7 +6732,7 @@
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
     </row>
-    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="15">
         <v>44873</v>
       </c>
@@ -6775,7 +6775,7 @@
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
     </row>
-    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="15">
         <v>44873</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
     </row>
-    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="15">
         <v>44873</v>
       </c>
@@ -6863,7 +6863,7 @@
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
     </row>
-    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="15">
         <v>44873</v>
       </c>
@@ -6908,7 +6908,7 @@
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
     </row>
-    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="15">
         <v>44873</v>
       </c>
@@ -6951,7 +6951,7 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
-    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="15">
         <v>44874</v>
       </c>
@@ -6996,7 +6996,7 @@
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
     </row>
-    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="15">
         <v>44874</v>
       </c>
@@ -7039,7 +7039,7 @@
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
     </row>
-    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="15">
         <v>44874</v>
       </c>
@@ -7084,7 +7084,7 @@
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
     </row>
-    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="15">
         <v>44874</v>
       </c>
@@ -7127,7 +7127,7 @@
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
     </row>
-    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="15">
         <v>44874</v>
       </c>
@@ -7172,7 +7172,7 @@
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
     </row>
-    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="15">
         <v>44874</v>
       </c>
@@ -7215,7 +7215,7 @@
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
     </row>
-    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="15">
         <v>44873</v>
       </c>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="W66" s="1"/>
     </row>
-    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="15">
         <v>44873</v>
       </c>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="W67" s="1"/>
     </row>
-    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="15">
         <v>44873</v>
       </c>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="W68" s="1"/>
     </row>
-    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15">
         <v>44873</v>
       </c>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="W69" s="1"/>
     </row>
-    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="15">
         <v>44873</v>
       </c>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="W70" s="1"/>
     </row>
-    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="15">
         <v>44873</v>
       </c>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="W71" s="1"/>
     </row>
-    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="15">
         <v>44873</v>
       </c>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="W72" s="1"/>
     </row>
-    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="15">
         <v>44873</v>
       </c>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="W73" s="1"/>
     </row>
-    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="15">
         <v>44873</v>
       </c>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="W74" s="1"/>
     </row>
-    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="15">
         <v>44873</v>
       </c>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="W75" s="1"/>
     </row>
-    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="15">
         <v>44874</v>
       </c>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W76" s="1"/>
     </row>
-    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="15">
         <v>44874</v>
       </c>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="W77" s="1"/>
     </row>
-    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="15">
         <v>44874</v>
       </c>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="W78" s="1"/>
     </row>
-    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="15">
         <v>44874</v>
       </c>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="W79" s="1"/>
     </row>
-    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="15">
         <v>44874</v>
       </c>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="W80" s="1"/>
     </row>
-    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="15">
         <v>44874</v>
       </c>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="W81" s="1"/>
     </row>
-    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="15">
         <v>45097</v>
       </c>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="W82" s="1"/>
     </row>
-    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="15">
         <v>45097</v>
       </c>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="W83" s="1"/>
     </row>
-    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="15">
         <v>45097</v>
       </c>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="W84" s="1"/>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="15">
         <v>45097</v>
       </c>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="W85" s="1"/>
     </row>
-    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="15">
         <v>45097</v>
       </c>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="W86" s="1"/>
     </row>
-    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="15">
         <v>45098</v>
       </c>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="W87" s="1"/>
     </row>
-    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="15">
         <v>45098</v>
       </c>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="W88" s="1"/>
     </row>
-    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="15">
         <v>45098</v>
       </c>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="W89" s="1"/>
     </row>
-    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="15">
         <v>45098</v>
       </c>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="W90" s="1"/>
     </row>
-    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="15">
         <v>45098</v>
       </c>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="W91" s="1"/>
     </row>
-    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="15">
         <v>45098</v>
       </c>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="W92" s="1"/>
     </row>
-    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="15">
         <v>45098</v>
       </c>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="W93" s="1"/>
     </row>
-    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="15">
         <v>45098</v>
       </c>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="W94" s="1"/>
     </row>
-    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="15">
         <v>45098</v>
       </c>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="W95" s="1"/>
     </row>
-    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="15">
         <v>45098</v>
       </c>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="W96" s="1"/>
     </row>
-    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="15">
         <v>45098</v>
       </c>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W97" s="1"/>
     </row>
-    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="15">
         <v>45099</v>
       </c>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="W98" s="1"/>
     </row>
-    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="15">
         <v>45099</v>
       </c>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="W99" s="1"/>
     </row>
-    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="15">
         <v>45099</v>
       </c>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="W100" s="1"/>
     </row>
-    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="15">
         <v>45099</v>
       </c>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="W101" s="1"/>
     </row>
-    <row r="102" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A102" s="16">
         <v>45189</v>
       </c>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="W102" s="2"/>
     </row>
-    <row r="103" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A103" s="16">
         <v>45189</v>
       </c>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="W103" s="2"/>
     </row>
-    <row r="104" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A104" s="16">
         <v>45189</v>
       </c>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="W104" s="2"/>
     </row>
-    <row r="105" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A105" s="16">
         <v>45189</v>
       </c>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="W105" s="2"/>
     </row>
-    <row r="106" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A106" s="16">
         <v>45189</v>
       </c>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="W106" s="2"/>
     </row>
-    <row r="107" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A107" s="16">
         <v>45189</v>
       </c>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="W107" s="2"/>
     </row>
-    <row r="108" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A108" s="16">
         <v>45189</v>
       </c>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="W108" s="2"/>
     </row>
-    <row r="109" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A109" s="16">
         <v>45189</v>
       </c>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="W109" s="2"/>
     </row>
-    <row r="110" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A110" s="16">
         <v>45189</v>
       </c>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="W110" s="2"/>
     </row>
-    <row r="111" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A111" s="17">
         <v>45189</v>
       </c>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="W111" s="2"/>
     </row>
-    <row r="112" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A112" s="17">
         <v>45189</v>
       </c>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="W112" s="2"/>
     </row>
-    <row r="113" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A113" s="17">
         <v>45189</v>
       </c>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="W113" s="2"/>
     </row>
-    <row r="114" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A114" s="17">
         <v>45189</v>
       </c>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W114" s="2"/>
     </row>
-    <row r="115" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A115" s="17">
         <v>45189</v>
       </c>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="W115" s="2"/>
     </row>
-    <row r="116" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A116" s="17">
         <v>45189</v>
       </c>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="W116" s="2"/>
     </row>
-    <row r="117" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A117" s="17">
         <v>45189</v>
       </c>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="W117" s="2"/>
     </row>
-    <row r="118" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A118" s="16">
         <v>45189</v>
       </c>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="W118" s="2"/>
     </row>
-    <row r="119" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A119" s="16">
         <v>45189</v>
       </c>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="W119" s="2"/>
     </row>
-    <row r="120" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A120" s="16">
         <v>45189</v>
       </c>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="W120" s="2"/>
     </row>
-    <row r="121" spans="1:23" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A121" s="16">
         <v>45189</v>
       </c>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="W121" s="2"/>
     </row>
-    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="15">
         <v>45342</v>
       </c>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="W122" s="1"/>
     </row>
-    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="15">
         <v>45342</v>
       </c>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="W123" s="1"/>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="23">
         <v>45342</v>
       </c>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="W124" s="1"/>
     </row>
-    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="15">
         <v>45342</v>
       </c>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="W125" s="1"/>
     </row>
-    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="15">
         <v>45342</v>
       </c>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="W126" s="1"/>
     </row>
-    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="15">
         <v>45342</v>
       </c>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="W127" s="1"/>
     </row>
-    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="15">
         <v>45342</v>
       </c>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="W128" s="1"/>
     </row>
-    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="15">
         <v>45342</v>
       </c>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="W129" s="1"/>
     </row>
-    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="15">
         <v>45342</v>
       </c>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="W130" s="1"/>
     </row>
-    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="15">
         <v>45342</v>
       </c>
@@ -11453,7 +11453,7 @@
       </c>
       <c r="W131" s="1"/>
     </row>
-    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="15">
         <v>45342</v>
       </c>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="W132" s="1"/>
     </row>
-    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="15">
         <v>45342</v>
       </c>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="W133" s="1"/>
     </row>
-    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="15">
         <v>45343</v>
       </c>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="W134" s="1"/>
     </row>
-    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="15">
         <v>45343</v>
       </c>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="W135" s="1"/>
     </row>
-    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="15">
         <v>45343</v>
       </c>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="W136" s="1"/>
     </row>
-    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="15">
         <v>45343</v>
       </c>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="W137" s="1"/>
     </row>
-    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="15">
         <v>45343</v>
       </c>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="W138" s="1"/>
     </row>
-    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="15">
         <v>45343</v>
       </c>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="W139" s="1"/>
     </row>
-    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="15">
         <v>45343</v>
       </c>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="W140" s="1"/>
     </row>
-    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="15">
         <v>45343</v>
       </c>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="W141" s="1"/>
     </row>
-    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="15">
         <v>45477</v>
       </c>
@@ -12161,7 +12161,7 @@
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
     </row>
-    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="15">
         <v>45477</v>
       </c>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="W143" s="1"/>
     </row>
-    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="15">
         <v>45477</v>
       </c>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="15">
         <v>45477</v>
       </c>
@@ -12346,7 +12346,7 @@
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
     </row>
-    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="15">
         <v>45477</v>
       </c>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="W146" s="1"/>
     </row>
-    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="15">
         <v>45477</v>
       </c>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="W147" s="1"/>
     </row>
-    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="15">
         <v>45477</v>
       </c>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="W148" s="1"/>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="15">
         <v>45477</v>
       </c>
@@ -12591,7 +12591,7 @@
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
     </row>
-    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="15">
         <v>45477</v>
       </c>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="W150" s="1"/>
     </row>
-    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="15">
         <v>45477</v>
       </c>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="W151" s="1"/>
     </row>
-    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="15">
         <v>45477</v>
       </c>
@@ -12776,7 +12776,7 @@
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
     </row>
-    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="15">
         <v>45477</v>
       </c>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="W153" s="1"/>
     </row>
-    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="15">
         <v>45477</v>
       </c>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="W154" s="1"/>
     </row>
-    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="15">
         <v>45477</v>
       </c>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="W155" s="1"/>
     </row>
-    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="15">
         <v>45477</v>
       </c>
@@ -13018,7 +13018,7 @@
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
     </row>
-    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="15">
         <v>45477</v>
       </c>
@@ -13077,7 +13077,7 @@
       </c>
       <c r="W157" s="1"/>
     </row>
-    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="15">
         <v>45477</v>
       </c>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="W158" s="1"/>
     </row>
-    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="15">
         <v>45477</v>
       </c>
@@ -13203,7 +13203,7 @@
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
     </row>
-    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="15">
         <v>45477</v>
       </c>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="W160" s="1"/>
     </row>
-    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="15">
         <v>45477</v>
       </c>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="W161" s="1"/>
     </row>
-    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="15">
         <v>45477</v>
       </c>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="W162" s="1"/>
     </row>
-    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="15">
         <v>45477</v>
       </c>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="W163" s="1"/>
     </row>
-    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="15">
         <v>45477</v>
       </c>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="W164" s="1"/>
     </row>
-    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="15">
         <v>45477</v>
       </c>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W165" s="1"/>
     </row>
-    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="15">
         <v>45477</v>
       </c>
@@ -13632,7 +13632,7 @@
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
     </row>
-    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="15">
         <v>45477</v>
       </c>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="W167" s="1"/>
     </row>
-    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="15">
         <v>45477</v>
       </c>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="W168" s="1"/>
     </row>
-    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="15">
         <v>45477</v>
       </c>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="W169" s="1"/>
     </row>
-    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="15">
         <v>45595</v>
       </c>
@@ -13874,7 +13874,7 @@
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
     </row>
-    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="15">
         <v>45595</v>
       </c>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="W171" s="1"/>
     </row>
-    <row r="172" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="15">
         <v>45595</v>
       </c>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="W172" s="1"/>
     </row>
-    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="15">
         <v>45595</v>
       </c>
@@ -14059,7 +14059,7 @@
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
     </row>
-    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="15">
         <v>45595</v>
       </c>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="W174" s="1"/>
     </row>
-    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="15">
         <v>45595</v>
       </c>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="W175" s="1"/>
     </row>
-    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="15">
         <v>45595</v>
       </c>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="W176" s="1"/>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="15">
         <v>45595</v>
       </c>
@@ -14304,7 +14304,7 @@
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
     </row>
-    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="15">
         <v>45595</v>
       </c>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="W178" s="1"/>
     </row>
-    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="15">
         <v>45595</v>
       </c>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="W179" s="1"/>
     </row>
-    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="15">
         <v>45595</v>
       </c>
@@ -14489,7 +14489,7 @@
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
     </row>
-    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="15">
         <v>45595</v>
       </c>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="W181" s="1"/>
     </row>
-    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="15">
         <v>45595</v>
       </c>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="W182" s="1"/>
     </row>
-    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="15">
         <v>45595</v>
       </c>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="W183" s="1"/>
     </row>
-    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="15">
         <v>45595</v>
       </c>
@@ -14731,7 +14731,7 @@
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
     </row>
-    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="15">
         <v>45595</v>
       </c>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="W185" s="1"/>
     </row>
-    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="15">
         <v>45595</v>
       </c>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="W186" s="1"/>
     </row>
-    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="15">
         <v>45595</v>
       </c>
@@ -14916,7 +14916,7 @@
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
     </row>
-    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="15">
         <v>45595</v>
       </c>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="W188" s="1"/>
     </row>
-    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="15">
         <v>45595</v>
       </c>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="W189" s="1"/>
     </row>
-    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="15">
         <v>45595</v>
       </c>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="W190" s="1"/>
     </row>
-    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="15">
         <v>45595</v>
       </c>
@@ -15158,7 +15158,7 @@
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
     </row>
-    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="15">
         <v>45595</v>
       </c>
@@ -15217,7 +15217,7 @@
       </c>
       <c r="W192" s="1"/>
     </row>
-    <row r="193" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="15">
         <v>45595</v>
       </c>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="W193" s="1"/>
     </row>
-    <row r="194" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="15">
         <v>45595</v>
       </c>
@@ -15343,7 +15343,7 @@
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
     </row>
-    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="15">
         <v>45595</v>
       </c>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="W195" s="1"/>
     </row>
-    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="15">
         <v>45595</v>
       </c>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="W196" s="1"/>
     </row>
-    <row r="197" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="15">
         <v>45595</v>
       </c>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="W197" s="1"/>
     </row>
-    <row r="198" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="15">
         <v>45685</v>
       </c>
@@ -15585,7 +15585,7 @@
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
     </row>
-    <row r="199" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="15">
         <v>45685</v>
       </c>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="W199" s="1"/>
     </row>
-    <row r="200" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="15">
         <v>45685</v>
       </c>
@@ -15703,7 +15703,7 @@
       </c>
       <c r="W200" s="1"/>
     </row>
-    <row r="201" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="15">
         <v>45685</v>
       </c>
@@ -15770,7 +15770,7 @@
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
     </row>
-    <row r="202" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="15">
         <v>45685</v>
       </c>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="W202" s="1"/>
     </row>
-    <row r="203" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="15">
         <v>45685</v>
       </c>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="W203" s="1"/>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="15">
         <v>45685</v>
       </c>
@@ -15955,7 +15955,7 @@
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
     </row>
-    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="15">
         <v>45685</v>
       </c>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="W205" s="1"/>
     </row>
-    <row r="206" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="15">
         <v>45685</v>
       </c>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="W206" s="1"/>
     </row>
-    <row r="207" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="15">
         <v>45685</v>
       </c>
@@ -16140,7 +16140,7 @@
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
     </row>
-    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="15">
         <v>45685</v>
       </c>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="W208" s="1"/>
     </row>
-    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="15">
         <v>45685</v>
       </c>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="W209" s="1"/>
     </row>
-    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="15">
         <v>45685</v>
       </c>
@@ -16325,7 +16325,7 @@
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
     </row>
-    <row r="211" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="15">
         <v>45685</v>
       </c>
@@ -16382,7 +16382,7 @@
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
     </row>
-    <row r="212" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="15">
         <v>45685</v>
       </c>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="W212" s="1"/>
     </row>
-    <row r="213" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="15">
         <v>45685</v>
       </c>
@@ -16508,7 +16508,7 @@
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
     </row>
-    <row r="214" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="15">
         <v>45685</v>
       </c>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="W214" s="1"/>
     </row>
-    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="15">
         <v>45685</v>
       </c>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="W215" s="1"/>
     </row>
-    <row r="216" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="15">
         <v>45685</v>
       </c>
@@ -16693,7 +16693,7 @@
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
     </row>
-    <row r="217" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="15">
         <v>45685</v>
       </c>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="W217" s="1"/>
     </row>
-    <row r="218" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="15">
         <v>45685</v>
       </c>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="W218" s="1"/>
     </row>
-    <row r="219" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="15">
         <v>45685</v>
       </c>
@@ -16878,7 +16878,7 @@
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
     </row>
-    <row r="220" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="15">
         <v>45685</v>
       </c>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="W220" s="1"/>
     </row>
-    <row r="221" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="15">
         <v>45685</v>
       </c>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="W221" s="1"/>
     </row>
-    <row r="222" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="15">
         <v>45824</v>
       </c>
@@ -17061,7 +17061,7 @@
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
     </row>
-    <row r="223" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="15"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="W223" s="1"/>
     </row>
-    <row r="224" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="15"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="W224" s="1"/>
     </row>
-    <row r="225" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="15">
         <v>45824</v>
       </c>
@@ -17234,7 +17234,7 @@
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
     </row>
-    <row r="226" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="15"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="W226" s="1"/>
     </row>
-    <row r="227" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="15"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="W227" s="1"/>
     </row>
-    <row r="228" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="15"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="W228" s="1"/>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="15">
         <v>45824</v>
       </c>
@@ -17458,7 +17458,7 @@
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
     </row>
-    <row r="230" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="15"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="W230" s="1"/>
     </row>
-    <row r="231" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="15"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="W231" s="1"/>
     </row>
-    <row r="232" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="15">
         <v>45824</v>
       </c>
@@ -17631,7 +17631,7 @@
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
     </row>
-    <row r="233" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="15"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="W233" s="1"/>
     </row>
-    <row r="234" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="15"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="W234" s="1"/>
     </row>
-    <row r="235" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="15"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="W235" s="1"/>
     </row>
-    <row r="236" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="15">
         <v>45824</v>
       </c>
@@ -17855,7 +17855,7 @@
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
     </row>
-    <row r="237" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="15"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -17908,7 +17908,7 @@
       </c>
       <c r="W237" s="1"/>
     </row>
-    <row r="238" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="15"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="W238" s="1"/>
     </row>
-    <row r="239" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="15">
         <v>45824</v>
       </c>
@@ -18028,7 +18028,7 @@
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
     </row>
-    <row r="240" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="15"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="W240" s="1"/>
     </row>
-    <row r="241" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="15"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="W241" s="1"/>
     </row>
-    <row r="242" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="15"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -18179,7 +18179,7 @@
       </c>
       <c r="W242" s="1"/>
     </row>
-    <row r="243" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="15">
         <v>45824</v>
       </c>
@@ -18246,7 +18246,7 @@
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
     </row>
-    <row r="244" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="15"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -18299,7 +18299,7 @@
       </c>
       <c r="W244" s="1"/>
     </row>
-    <row r="245" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="15"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="W245" s="1"/>
     </row>
-    <row r="246" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="15">
         <v>45824</v>
       </c>
@@ -18419,7 +18419,7 @@
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
     </row>
-    <row r="247" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="15"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -18472,7 +18472,7 @@
       </c>
       <c r="W247" s="1"/>
     </row>
-    <row r="248" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="15"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -18525,7 +18525,7 @@
       </c>
       <c r="W248" s="1"/>
     </row>
-    <row r="249" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="15"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -18576,7 +18576,7 @@
       </c>
       <c r="W249" s="1"/>
     </row>
-    <row r="250" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="15">
         <v>45868</v>
       </c>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="W250" s="1"/>
     </row>
-    <row r="251" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="15">
         <v>45868</v>
       </c>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="W251" s="1"/>
     </row>
-    <row r="252" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="15">
         <v>45868</v>
       </c>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="W252" s="1"/>
     </row>
-    <row r="253" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="15">
         <v>45868</v>
       </c>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="W253" s="1"/>
     </row>
-    <row r="254" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="15">
         <v>45868</v>
       </c>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="W254" s="1"/>
     </row>
-    <row r="255" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="15">
         <v>45868</v>
       </c>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="W255" s="1"/>
     </row>
-    <row r="256" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="15">
         <v>45868</v>
       </c>
@@ -19015,7 +19015,7 @@
       </c>
       <c r="W256" s="1"/>
     </row>
-    <row r="257" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="15">
         <v>45868</v>
       </c>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="W257" s="1"/>
     </row>
-    <row r="258" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="15">
         <v>45868</v>
       </c>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="W258" s="1"/>
     </row>
-    <row r="259" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="15">
         <v>45868</v>
       </c>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="W259" s="1"/>
     </row>
-    <row r="260" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="15">
         <v>45868</v>
       </c>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="W260" s="1"/>
     </row>
-    <row r="261" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="15">
         <v>45868</v>
       </c>
@@ -19328,7 +19328,7 @@
       </c>
       <c r="W261" s="1"/>
     </row>
-    <row r="262" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="15">
         <v>45868</v>
       </c>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="W262" s="1"/>
     </row>
-    <row r="263" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="15">
         <v>45868</v>
       </c>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="W263" s="1"/>
     </row>
-    <row r="264" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="15">
         <v>45868</v>
       </c>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="W264" s="1"/>
     </row>
-    <row r="265" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="15">
         <v>45868</v>
       </c>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="W265" s="1"/>
     </row>
-    <row r="266" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="15">
         <v>45868</v>
       </c>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="W266" s="1"/>
     </row>
-    <row r="267" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="15">
         <v>45868</v>
       </c>
@@ -19704,7 +19704,7 @@
       </c>
       <c r="W267" s="1"/>
     </row>
-    <row r="268" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="15">
         <v>45868</v>
       </c>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="W268" s="1"/>
     </row>
-    <row r="269" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="15">
         <v>45868</v>
       </c>
@@ -19828,7 +19828,7 @@
       </c>
       <c r="W269" s="1"/>
     </row>
-    <row r="270" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="15">
         <v>45477</v>
       </c>
@@ -19895,7 +19895,7 @@
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
     </row>
-    <row r="271" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="15">
         <v>45477</v>
       </c>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="W271" s="1"/>
     </row>
-    <row r="272" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="15">
         <v>45477</v>
       </c>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="W272" s="1"/>
     </row>
-    <row r="273" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="15">
         <v>45477</v>
       </c>
@@ -20080,7 +20080,7 @@
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
     </row>
-    <row r="274" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="15">
         <v>45477</v>
       </c>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="W274" s="1"/>
     </row>
-    <row r="275" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="15">
         <v>45477</v>
       </c>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="W275" s="1"/>
     </row>
-    <row r="276" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="15">
         <v>45477</v>
       </c>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="W276" s="1"/>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="15">
         <v>45477</v>
       </c>
@@ -20320,7 +20320,7 @@
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
     </row>
-    <row r="278" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="15">
         <v>45477</v>
       </c>
@@ -20379,7 +20379,7 @@
       </c>
       <c r="W278" s="1"/>
     </row>
-    <row r="279" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="15">
         <v>45477</v>
       </c>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="W279" s="1"/>
     </row>
-    <row r="280" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="15">
         <v>45477</v>
       </c>
@@ -20505,7 +20505,7 @@
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
     </row>
-    <row r="281" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="15">
         <v>45477</v>
       </c>
@@ -20564,7 +20564,7 @@
       </c>
       <c r="W281" s="1"/>
     </row>
-    <row r="282" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="15">
         <v>45477</v>
       </c>
@@ -20623,7 +20623,7 @@
       </c>
       <c r="W282" s="1"/>
     </row>
-    <row r="283" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="15">
         <v>45477</v>
       </c>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="W283" s="1"/>
     </row>
-    <row r="284" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="15">
         <v>45477</v>
       </c>
@@ -20747,7 +20747,7 @@
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
     </row>
-    <row r="285" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="15">
         <v>45477</v>
       </c>
@@ -20806,7 +20806,7 @@
       </c>
       <c r="W285" s="1"/>
     </row>
-    <row r="286" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="15">
         <v>45477</v>
       </c>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="W286" s="1"/>
     </row>
-    <row r="287" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="15">
         <v>45477</v>
       </c>
@@ -20932,7 +20932,7 @@
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
     </row>
-    <row r="288" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="15">
         <v>45477</v>
       </c>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="W288" s="1"/>
     </row>
-    <row r="289" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="15">
         <v>45477</v>
       </c>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="W289" s="1"/>
     </row>
-    <row r="290" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="15">
         <v>45477</v>
       </c>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="W290" s="1"/>
     </row>
-    <row r="291" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="15">
         <v>45477</v>
       </c>
@@ -21176,7 +21176,7 @@
       </c>
       <c r="W291" s="1"/>
     </row>
-    <row r="292" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="15">
         <v>45477</v>
       </c>
@@ -21235,7 +21235,7 @@
       </c>
       <c r="W292" s="1"/>
     </row>
-    <row r="293" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="15">
         <v>45477</v>
       </c>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="W293" s="1"/>
     </row>
-    <row r="294" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="15">
         <v>45477</v>
       </c>
@@ -21361,7 +21361,7 @@
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
     </row>
-    <row r="295" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="15">
         <v>45477</v>
       </c>
@@ -21420,7 +21420,7 @@
       </c>
       <c r="W295" s="1"/>
     </row>
-    <row r="296" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="15">
         <v>45477</v>
       </c>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="W296" s="1"/>
     </row>
-    <row r="297" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="15">
         <v>45477</v>
       </c>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="W297" s="1"/>
     </row>
-    <row r="298" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="15">
         <v>45595</v>
       </c>
@@ -21603,7 +21603,7 @@
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
     </row>
-    <row r="299" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="15">
         <v>45595</v>
       </c>
@@ -21662,7 +21662,7 @@
       </c>
       <c r="W299" s="1"/>
     </row>
-    <row r="300" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="15">
         <v>45595</v>
       </c>
@@ -21721,7 +21721,7 @@
       </c>
       <c r="W300" s="1"/>
     </row>
-    <row r="301" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="15">
         <v>45595</v>
       </c>
@@ -21788,7 +21788,7 @@
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
     </row>
-    <row r="302" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="15">
         <v>45595</v>
       </c>
@@ -21847,7 +21847,7 @@
       </c>
       <c r="W302" s="1"/>
     </row>
-    <row r="303" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="15">
         <v>45595</v>
       </c>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="W303" s="1"/>
     </row>
-    <row r="304" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="15">
         <v>45595</v>
       </c>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="W304" s="1"/>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="15">
         <v>45595</v>
       </c>
@@ -22030,7 +22030,7 @@
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
     </row>
-    <row r="306" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="15">
         <v>45595</v>
       </c>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="W306" s="1"/>
     </row>
-    <row r="307" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="15">
         <v>45595</v>
       </c>
@@ -22144,7 +22144,7 @@
       </c>
       <c r="W307" s="1"/>
     </row>
-    <row r="308" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="15">
         <v>45595</v>
       </c>
@@ -22211,7 +22211,7 @@
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
     </row>
-    <row r="309" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="15">
         <v>45595</v>
       </c>
@@ -22268,7 +22268,7 @@
       </c>
       <c r="W309" s="1"/>
     </row>
-    <row r="310" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="15">
         <v>45595</v>
       </c>
@@ -22325,7 +22325,7 @@
       </c>
       <c r="W310" s="1"/>
     </row>
-    <row r="311" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="15">
         <v>45595</v>
       </c>
@@ -22380,7 +22380,7 @@
       </c>
       <c r="W311" s="1"/>
     </row>
-    <row r="312" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="15">
         <v>45595</v>
       </c>
@@ -22447,7 +22447,7 @@
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
     </row>
-    <row r="313" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="15">
         <v>45595</v>
       </c>
@@ -22504,7 +22504,7 @@
       </c>
       <c r="W313" s="1"/>
     </row>
-    <row r="314" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="15">
         <v>45595</v>
       </c>
@@ -22561,7 +22561,7 @@
       </c>
       <c r="W314" s="1"/>
     </row>
-    <row r="315" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="15">
         <v>45595</v>
       </c>
@@ -22628,7 +22628,7 @@
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
     </row>
-    <row r="316" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="15">
         <v>45595</v>
       </c>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="W316" s="1"/>
     </row>
-    <row r="317" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="15">
         <v>45595</v>
       </c>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="W317" s="1"/>
     </row>
-    <row r="318" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="15">
         <v>45595</v>
       </c>
@@ -22797,7 +22797,7 @@
       </c>
       <c r="W318" s="1"/>
     </row>
-    <row r="319" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="15">
         <v>45595</v>
       </c>
@@ -22864,7 +22864,7 @@
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
     </row>
-    <row r="320" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="15">
         <v>45595</v>
       </c>
@@ -22923,7 +22923,7 @@
       </c>
       <c r="W320" s="1"/>
     </row>
-    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="15">
         <v>45595</v>
       </c>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="W321" s="1"/>
     </row>
-    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="15">
         <v>45595</v>
       </c>
@@ -23049,7 +23049,7 @@
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
     </row>
-    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="15">
         <v>45595</v>
       </c>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="W323" s="1"/>
     </row>
-    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="15">
         <v>45595</v>
       </c>
@@ -23167,7 +23167,7 @@
       </c>
       <c r="W324" s="1"/>
     </row>
-    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="15">
         <v>45595</v>
       </c>
@@ -23224,7 +23224,7 @@
       </c>
       <c r="W325" s="1"/>
     </row>
-    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="15">
         <v>45685</v>
       </c>
@@ -23291,7 +23291,7 @@
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
     </row>
-    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="15">
         <v>45685</v>
       </c>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="W327" s="1"/>
     </row>
-    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="15">
         <v>45685</v>
       </c>
@@ -23409,7 +23409,7 @@
       </c>
       <c r="W328" s="1"/>
     </row>
-    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="15">
         <v>45685</v>
       </c>
@@ -23476,7 +23476,7 @@
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
     </row>
-    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="15">
         <v>45685</v>
       </c>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="W330" s="1"/>
     </row>
-    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="15">
         <v>45685</v>
       </c>
@@ -23594,7 +23594,7 @@
       </c>
       <c r="W331" s="1"/>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="15">
         <v>45685</v>
       </c>
@@ -23661,7 +23661,7 @@
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
     </row>
-    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="15">
         <v>45685</v>
       </c>
@@ -23720,7 +23720,7 @@
       </c>
       <c r="W333" s="1"/>
     </row>
-    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="15">
         <v>45685</v>
       </c>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="W334" s="1"/>
     </row>
-    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="15">
         <v>45685</v>
       </c>
@@ -23846,7 +23846,7 @@
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
     </row>
-    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="15">
         <v>45685</v>
       </c>
@@ -23905,7 +23905,7 @@
       </c>
       <c r="W336" s="1"/>
     </row>
-    <row r="337" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="15">
         <v>45685</v>
       </c>
@@ -23964,7 +23964,7 @@
       </c>
       <c r="W337" s="1"/>
     </row>
-    <row r="338" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="15">
         <v>45685</v>
       </c>
@@ -24031,7 +24031,7 @@
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
     </row>
-    <row r="339" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="15">
         <v>45685</v>
       </c>
@@ -24088,7 +24088,7 @@
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
     </row>
-    <row r="340" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="15">
         <v>45685</v>
       </c>
@@ -24145,7 +24145,7 @@
       </c>
       <c r="W340" s="1"/>
     </row>
-    <row r="341" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="15">
         <v>45685</v>
       </c>
@@ -24212,7 +24212,7 @@
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
     </row>
-    <row r="342" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="15">
         <v>45685</v>
       </c>
@@ -24271,7 +24271,7 @@
       </c>
       <c r="W342" s="1"/>
     </row>
-    <row r="343" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="15">
         <v>45685</v>
       </c>
@@ -24330,7 +24330,7 @@
       </c>
       <c r="W343" s="1"/>
     </row>
-    <row r="344" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="15">
         <v>45685</v>
       </c>
@@ -24397,7 +24397,7 @@
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
     </row>
-    <row r="345" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="15">
         <v>45685</v>
       </c>
@@ -24456,7 +24456,7 @@
       </c>
       <c r="W345" s="1"/>
     </row>
-    <row r="346" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="15">
         <v>45685</v>
       </c>
@@ -24515,7 +24515,7 @@
       </c>
       <c r="W346" s="1"/>
     </row>
-    <row r="347" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="15">
         <v>45685</v>
       </c>
@@ -24582,7 +24582,7 @@
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
     </row>
-    <row r="348" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="15">
         <v>45685</v>
       </c>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="W348" s="1"/>
     </row>
-    <row r="349" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="15">
         <v>45685</v>
       </c>
@@ -24698,7 +24698,7 @@
       </c>
       <c r="W349" s="1"/>
     </row>
-    <row r="350" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="15">
         <v>45741</v>
       </c>
@@ -24765,7 +24765,7 @@
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
     </row>
-    <row r="351" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="15"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -24818,7 +24818,7 @@
       </c>
       <c r="W351" s="1"/>
     </row>
-    <row r="352" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="15"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -24871,7 +24871,7 @@
       </c>
       <c r="W352" s="1"/>
     </row>
-    <row r="353" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="15">
         <v>45741</v>
       </c>
@@ -24938,7 +24938,7 @@
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
     </row>
-    <row r="354" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="15"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="W354" s="1"/>
     </row>
-    <row r="355" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="15"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -25042,7 +25042,7 @@
       </c>
       <c r="W355" s="1"/>
     </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="15">
         <v>45741</v>
       </c>
@@ -25109,7 +25109,7 @@
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
     </row>
-    <row r="357" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="15"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -25160,7 +25160,7 @@
       </c>
       <c r="W357" s="1"/>
     </row>
-    <row r="358" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="15"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -25211,7 +25211,7 @@
       </c>
       <c r="W358" s="1"/>
     </row>
-    <row r="359" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="15">
         <v>45741</v>
       </c>
@@ -25278,7 +25278,7 @@
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
     </row>
-    <row r="360" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="15"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -25329,7 +25329,7 @@
       </c>
       <c r="W360" s="1"/>
     </row>
-    <row r="361" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="15"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -25380,7 +25380,7 @@
       </c>
       <c r="W361" s="1"/>
     </row>
-    <row r="362" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="15">
         <v>45741</v>
       </c>
@@ -25447,7 +25447,7 @@
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
     </row>
-    <row r="363" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="15"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="W363" s="1"/>
     </row>
-    <row r="364" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="15"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="W364" s="1"/>
     </row>
-    <row r="365" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="15">
         <v>45741</v>
       </c>
@@ -25616,7 +25616,7 @@
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
     </row>
-    <row r="366" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="15"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -25667,7 +25667,7 @@
       </c>
       <c r="W366" s="1"/>
     </row>
-    <row r="367" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="15"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="W367" s="1"/>
     </row>
-    <row r="368" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="15">
         <v>45741</v>
       </c>
@@ -25785,7 +25785,7 @@
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
     </row>
-    <row r="369" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="15"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -25838,7 +25838,7 @@
       </c>
       <c r="W369" s="1"/>
     </row>
-    <row r="370" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="15"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="W370" s="1"/>
     </row>
-    <row r="371" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="15">
         <v>45741</v>
       </c>
@@ -25958,7 +25958,7 @@
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
     </row>
-    <row r="372" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="15"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="W372" s="1"/>
     </row>
-    <row r="373" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="15"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -26060,7 +26060,7 @@
       </c>
       <c r="W373" s="1"/>
     </row>
-    <row r="374" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="15">
         <v>45824</v>
       </c>
@@ -26127,7 +26127,7 @@
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
     </row>
-    <row r="375" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="15">
         <v>45824</v>
       </c>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="W375" s="1"/>
     </row>
-    <row r="376" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="15">
         <v>45824</v>
       </c>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="W376" s="1"/>
     </row>
-    <row r="377" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="15">
         <v>45824</v>
       </c>
@@ -26312,7 +26312,7 @@
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
     </row>
-    <row r="378" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="15">
         <v>45824</v>
       </c>
@@ -26371,7 +26371,7 @@
       </c>
       <c r="W378" s="1"/>
     </row>
-    <row r="379" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="15">
         <v>45824</v>
       </c>
@@ -26430,7 +26430,7 @@
       </c>
       <c r="W379" s="1"/>
     </row>
-    <row r="380" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="15">
         <v>45824</v>
       </c>
@@ -26487,7 +26487,7 @@
       </c>
       <c r="W380" s="1"/>
     </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="15">
         <v>45824</v>
       </c>
@@ -26554,7 +26554,7 @@
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
     </row>
-    <row r="382" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="15">
         <v>45824</v>
       </c>
@@ -26611,7 +26611,7 @@
       </c>
       <c r="W382" s="1"/>
     </row>
-    <row r="383" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="15">
         <v>45824</v>
       </c>
@@ -26668,7 +26668,7 @@
       </c>
       <c r="W383" s="1"/>
     </row>
-    <row r="384" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="15">
         <v>45824</v>
       </c>
@@ -26735,7 +26735,7 @@
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
     </row>
-    <row r="385" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="15">
         <v>45824</v>
       </c>
@@ -26794,7 +26794,7 @@
       </c>
       <c r="W385" s="1"/>
     </row>
-    <row r="386" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="15">
         <v>45824</v>
       </c>
@@ -26853,7 +26853,7 @@
       </c>
       <c r="W386" s="1"/>
     </row>
-    <row r="387" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="15">
         <v>45824</v>
       </c>
@@ -26910,7 +26910,7 @@
       </c>
       <c r="W387" s="1"/>
     </row>
-    <row r="388" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="15">
         <v>45824</v>
       </c>
@@ -26977,7 +26977,7 @@
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
     </row>
-    <row r="389" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="15">
         <v>45824</v>
       </c>
@@ -27034,7 +27034,7 @@
       </c>
       <c r="W389" s="1"/>
     </row>
-    <row r="390" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="15">
         <v>45824</v>
       </c>
@@ -27091,7 +27091,7 @@
       </c>
       <c r="W390" s="1"/>
     </row>
-    <row r="391" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="15">
         <v>45824</v>
       </c>
@@ -27158,7 +27158,7 @@
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
     </row>
-    <row r="392" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="15">
         <v>45824</v>
       </c>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="W392" s="1"/>
     </row>
-    <row r="393" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="15">
         <v>45824</v>
       </c>
@@ -27276,7 +27276,7 @@
       </c>
       <c r="W393" s="1"/>
     </row>
-    <row r="394" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="15">
         <v>45824</v>
       </c>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="W394" s="1"/>
     </row>
-    <row r="395" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="15">
         <v>45824</v>
       </c>
@@ -27398,7 +27398,7 @@
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
     </row>
-    <row r="396" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="15">
         <v>45824</v>
       </c>
@@ -27457,7 +27457,7 @@
       </c>
       <c r="W396" s="1"/>
     </row>
-    <row r="397" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="15">
         <v>45824</v>
       </c>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="W397" s="1"/>
     </row>
-    <row r="398" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="15">
         <v>45824</v>
       </c>
@@ -27581,7 +27581,7 @@
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
     </row>
-    <row r="399" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="15">
         <v>45824</v>
       </c>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="W399" s="1"/>
     </row>
-    <row r="400" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="15">
         <v>45824</v>
       </c>
@@ -27695,7 +27695,7 @@
       </c>
       <c r="W400" s="1"/>
     </row>
-    <row r="401" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="15">
         <v>45824</v>
       </c>
@@ -27750,7 +27750,7 @@
       </c>
       <c r="W401" s="1"/>
     </row>
-    <row r="402" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="15">
         <v>45868</v>
       </c>
@@ -27807,7 +27807,7 @@
       </c>
       <c r="W402" s="1"/>
     </row>
-    <row r="403" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="15">
         <v>45868</v>
       </c>
@@ -27864,7 +27864,7 @@
       </c>
       <c r="W403" s="1"/>
     </row>
-    <row r="404" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="15">
         <v>45868</v>
       </c>
@@ -27921,7 +27921,7 @@
       </c>
       <c r="W404" s="1"/>
     </row>
-    <row r="405" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="15">
         <v>45868</v>
       </c>
@@ -27978,7 +27978,7 @@
       </c>
       <c r="W405" s="1"/>
     </row>
-    <row r="406" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="15">
         <v>45868</v>
       </c>
@@ -28033,7 +28033,7 @@
       </c>
       <c r="W406" s="1"/>
     </row>
-    <row r="407" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="15">
         <v>45868</v>
       </c>
@@ -28090,7 +28090,7 @@
       </c>
       <c r="W407" s="1"/>
     </row>
-    <row r="408" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="15">
         <v>45868</v>
       </c>
@@ -28147,7 +28147,7 @@
       </c>
       <c r="W408" s="1"/>
     </row>
-    <row r="409" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="15">
         <v>45868</v>
       </c>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="W409" s="1"/>
     </row>
-    <row r="410" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="15">
         <v>45868</v>
       </c>
@@ -28261,7 +28261,7 @@
       </c>
       <c r="W410" s="1"/>
     </row>
-    <row r="411" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="15">
         <v>45868</v>
       </c>
@@ -28316,7 +28316,7 @@
       </c>
       <c r="W411" s="1"/>
     </row>
-    <row r="412" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" s="15">
         <v>45868</v>
       </c>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="W412" s="1"/>
     </row>
-    <row r="413" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="15">
         <v>45868</v>
       </c>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="W413" s="1"/>
     </row>
-    <row r="414" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" s="15">
         <v>45868</v>
       </c>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="W414" s="1"/>
     </row>
-    <row r="415" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" s="15">
         <v>45868</v>
       </c>
@@ -28544,7 +28544,7 @@
       </c>
       <c r="W415" s="1"/>
     </row>
-    <row r="416" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" s="15">
         <v>45868</v>
       </c>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="W416" s="1"/>
     </row>
-    <row r="417" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="15">
         <v>45868</v>
       </c>
@@ -28656,7 +28656,7 @@
       </c>
       <c r="W417" s="1"/>
     </row>
-    <row r="418" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" s="15">
         <v>45868</v>
       </c>
@@ -28713,7 +28713,7 @@
       </c>
       <c r="W418" s="1"/>
     </row>
-    <row r="419" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" s="15">
         <v>45868</v>
       </c>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="W419" s="1"/>
     </row>
-    <row r="420" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" s="15">
         <v>45868</v>
       </c>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="W420" s="1"/>
     </row>
-    <row r="421" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" s="15">
         <v>45868</v>
       </c>
@@ -28882,7 +28882,7 @@
       </c>
       <c r="W421" s="1"/>
     </row>
-    <row r="422" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" s="15"/>
       <c r="B422" s="1" t="s">
         <v>176</v>
@@ -28947,7 +28947,7 @@
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
     </row>
-    <row r="423" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" s="15"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -28998,7 +28998,7 @@
       </c>
       <c r="W423" s="1"/>
     </row>
-    <row r="424" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" s="15"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="W424" s="1"/>
     </row>
-    <row r="425" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" s="15"/>
       <c r="B425" s="1" t="s">
         <v>507</v>
@@ -29114,7 +29114,7 @@
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
     </row>
-    <row r="426" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" s="15"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -29165,7 +29165,7 @@
       </c>
       <c r="W426" s="1"/>
     </row>
-    <row r="427" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" s="15"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="W427" s="1"/>
     </row>
-    <row r="428" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" s="15"/>
       <c r="B428" s="1" t="s">
         <v>580</v>
@@ -29281,7 +29281,7 @@
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
     </row>
-    <row r="429" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" s="15"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -29332,7 +29332,7 @@
       </c>
       <c r="W429" s="1"/>
     </row>
-    <row r="430" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" s="15"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -29383,7 +29383,7 @@
       </c>
       <c r="W430" s="1"/>
     </row>
-    <row r="431" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" s="15"/>
       <c r="B431" s="1" t="s">
         <v>705</v>
@@ -29448,7 +29448,7 @@
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
     </row>
-    <row r="432" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" s="15"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="W432" s="1"/>
     </row>
-    <row r="433" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" s="15"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -29550,7 +29550,7 @@
       </c>
       <c r="W433" s="1"/>
     </row>
-    <row r="434" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" s="15"/>
       <c r="B434" s="1" t="s">
         <v>711</v>
@@ -29617,7 +29617,7 @@
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
     </row>
-    <row r="435" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" s="15"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -29666,7 +29666,7 @@
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
     </row>
-    <row r="436" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" s="15"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -29715,7 +29715,7 @@
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
     </row>
-    <row r="437" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" s="15"/>
       <c r="B437" s="1" t="s">
         <v>715</v>
@@ -29780,7 +29780,7 @@
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
     </row>
-    <row r="438" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" s="15"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -29831,7 +29831,7 @@
       </c>
       <c r="W438" s="1"/>
     </row>
-    <row r="439" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" s="15"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -29882,7 +29882,7 @@
       </c>
       <c r="W439" s="1"/>
     </row>
-    <row r="440" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" s="15"/>
       <c r="B440" s="1" t="s">
         <v>672</v>
@@ -29947,7 +29947,7 @@
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
     </row>
-    <row r="441" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" s="15"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="W441" s="1"/>
     </row>
-    <row r="442" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" s="15"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -30047,7 +30047,7 @@
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
     </row>
-    <row r="443" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" s="15"/>
       <c r="B443" s="1" t="s">
         <v>723</v>
@@ -30112,7 +30112,7 @@
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
     </row>
-    <row r="444" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" s="15"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="W444" s="1"/>
     </row>
-    <row r="445" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" s="15"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -30190,7 +30190,7 @@
       <c r="L445" s="1"/>
       <c r="M445" s="1"/>
       <c r="N445" s="1">
-        <f t="shared" ref="N406:N445" si="37">IF(ISBLANK(M445), IF(H445=0,0.9,0.27), M445)</f>
+        <f t="shared" ref="N445" si="37">IF(ISBLANK(M445), IF(H445=0,0.9,0.27), M445)</f>
         <v>0.9</v>
       </c>
       <c r="O445" s="1"/>
@@ -30235,22 +30235,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E99616-7BEB-4314-B7A1-02BCD6407201}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:M445"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.83984375" customWidth="1"/>
+    <col min="2" max="2" width="17.26171875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.26171875" customWidth="1"/>
+    <col min="6" max="6" width="27.26171875" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.83984375" customWidth="1"/>
+    <col min="9" max="9" width="26.83984375" customWidth="1"/>
+    <col min="10" max="10" width="17.15625" customWidth="1"/>
+    <col min="11" max="11" width="20.83984375" customWidth="1"/>
+    <col min="12" max="12" width="15.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -30291,7 +30291,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15">
         <v>44599</v>
       </c>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15">
         <v>44599</v>
       </c>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="15">
         <v>44600</v>
       </c>
@@ -30396,7 +30396,7 @@
       </c>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15">
         <v>44600</v>
       </c>
@@ -30431,7 +30431,7 @@
       </c>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="15">
         <v>44609</v>
       </c>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15">
         <v>44609</v>
       </c>
@@ -30505,7 +30505,7 @@
       </c>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15">
         <v>44609</v>
       </c>
@@ -30542,7 +30542,7 @@
       </c>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="15">
         <v>44609</v>
       </c>
@@ -30579,7 +30579,7 @@
       </c>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15">
         <v>44610</v>
       </c>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="15">
         <v>44610</v>
       </c>
@@ -30653,7 +30653,7 @@
       </c>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="15">
         <v>44610</v>
       </c>
@@ -30690,7 +30690,7 @@
       </c>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="15">
         <v>44610</v>
       </c>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="15">
         <v>44610</v>
       </c>
@@ -30764,7 +30764,7 @@
       </c>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="15">
         <v>44610</v>
       </c>
@@ -30801,7 +30801,7 @@
       </c>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="15">
         <v>44613</v>
       </c>
@@ -30838,7 +30838,7 @@
       </c>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="15">
         <v>44613</v>
       </c>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="15">
         <v>44615</v>
       </c>
@@ -30912,7 +30912,7 @@
       </c>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="15">
         <v>44615</v>
       </c>
@@ -30949,7 +30949,7 @@
       </c>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="15">
         <v>44615</v>
       </c>
@@ -30986,7 +30986,7 @@
       </c>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="15">
         <v>44615</v>
       </c>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="15">
         <v>44616</v>
       </c>
@@ -31060,7 +31060,7 @@
       </c>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="15">
         <v>44616</v>
       </c>
@@ -31097,7 +31097,7 @@
       </c>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="15">
         <v>44616</v>
       </c>
@@ -31134,7 +31134,7 @@
       </c>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="15">
         <v>44616</v>
       </c>
@@ -31171,7 +31171,7 @@
       </c>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="15">
         <v>44622</v>
       </c>
@@ -31208,7 +31208,7 @@
       </c>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="15">
         <v>44622</v>
       </c>
@@ -31245,7 +31245,7 @@
       </c>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="15">
         <v>44622</v>
       </c>
@@ -31282,7 +31282,7 @@
       </c>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="15">
         <v>44622</v>
       </c>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="15">
         <v>44622</v>
       </c>
@@ -31356,7 +31356,7 @@
       </c>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="15">
         <v>44622</v>
       </c>
@@ -31393,7 +31393,7 @@
       </c>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="15">
         <v>44622</v>
       </c>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="15">
         <v>44622</v>
       </c>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="M33" s="1"/>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="15">
         <v>44622</v>
       </c>
@@ -31504,7 +31504,7 @@
       </c>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="15">
         <v>44622</v>
       </c>
@@ -31541,7 +31541,7 @@
       </c>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="15">
         <v>44622</v>
       </c>
@@ -31578,7 +31578,7 @@
       </c>
       <c r="M36" s="1"/>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="15">
         <v>44622</v>
       </c>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="15">
         <v>44622</v>
       </c>
@@ -31652,7 +31652,7 @@
       </c>
       <c r="M38" s="1"/>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="15">
         <v>44622</v>
       </c>
@@ -31689,7 +31689,7 @@
       </c>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="15">
         <v>44622</v>
       </c>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="M40" s="1"/>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="15">
         <v>44622</v>
       </c>
@@ -31763,7 +31763,7 @@
       </c>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="15">
         <v>44599</v>
       </c>
@@ -31802,7 +31802,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="15">
         <v>44629</v>
       </c>
@@ -31841,7 +31841,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="15">
         <v>44629</v>
       </c>
@@ -31878,7 +31878,7 @@
       </c>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="15">
         <v>44629</v>
       </c>
@@ -31915,7 +31915,7 @@
       </c>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="15">
         <v>44629</v>
       </c>
@@ -31954,7 +31954,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="15">
         <v>44629</v>
       </c>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="15">
         <v>44630</v>
       </c>
@@ -32030,7 +32030,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="15">
         <v>44630</v>
       </c>
@@ -32067,7 +32067,7 @@
       </c>
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="15">
         <v>44873</v>
       </c>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="M50" s="1"/>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="15">
         <v>44873</v>
       </c>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="15">
         <v>44873</v>
       </c>
@@ -32156,7 +32156,7 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="15">
         <v>44873</v>
       </c>
@@ -32177,7 +32177,7 @@
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="15">
         <v>44873</v>
       </c>
@@ -32200,7 +32200,7 @@
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="15">
         <v>44873</v>
       </c>
@@ -32221,7 +32221,7 @@
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="15">
         <v>44873</v>
       </c>
@@ -32244,7 +32244,7 @@
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="15">
         <v>44873</v>
       </c>
@@ -32265,7 +32265,7 @@
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="15">
         <v>44873</v>
       </c>
@@ -32288,7 +32288,7 @@
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="15">
         <v>44873</v>
       </c>
@@ -32309,7 +32309,7 @@
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="15">
         <v>44874</v>
       </c>
@@ -32332,7 +32332,7 @@
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="15">
         <v>44874</v>
       </c>
@@ -32353,7 +32353,7 @@
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="15">
         <v>44874</v>
       </c>
@@ -32376,7 +32376,7 @@
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="15">
         <v>44874</v>
       </c>
@@ -32397,7 +32397,7 @@
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="15">
         <v>44874</v>
       </c>
@@ -32420,7 +32420,7 @@
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="15">
         <v>44874</v>
       </c>
@@ -32441,7 +32441,7 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="15">
         <v>44873</v>
       </c>
@@ -32478,7 +32478,7 @@
       </c>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="15">
         <v>44873</v>
       </c>
@@ -32513,7 +32513,7 @@
       </c>
       <c r="M67" s="1"/>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="15">
         <v>44873</v>
       </c>
@@ -32550,7 +32550,7 @@
       </c>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15">
         <v>44873</v>
       </c>
@@ -32585,7 +32585,7 @@
       </c>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="15">
         <v>44873</v>
       </c>
@@ -32622,7 +32622,7 @@
       </c>
       <c r="M70" s="1"/>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="15">
         <v>44873</v>
       </c>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="15">
         <v>44873</v>
       </c>
@@ -32694,7 +32694,7 @@
       </c>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="15">
         <v>44873</v>
       </c>
@@ -32729,7 +32729,7 @@
       </c>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="15">
         <v>44873</v>
       </c>
@@ -32766,7 +32766,7 @@
       </c>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="15">
         <v>44873</v>
       </c>
@@ -32801,7 +32801,7 @@
       </c>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="15">
         <v>44874</v>
       </c>
@@ -32838,7 +32838,7 @@
       </c>
       <c r="M76" s="1"/>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="15">
         <v>44874</v>
       </c>
@@ -32873,7 +32873,7 @@
       </c>
       <c r="M77" s="1"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="15">
         <v>44874</v>
       </c>
@@ -32910,7 +32910,7 @@
       </c>
       <c r="M78" s="1"/>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="15">
         <v>44874</v>
       </c>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="M79" s="1"/>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="15">
         <v>44874</v>
       </c>
@@ -32982,7 +32982,7 @@
       </c>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="15">
         <v>44874</v>
       </c>
@@ -33017,7 +33017,7 @@
       </c>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="15">
         <v>45097</v>
       </c>
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="15">
         <v>45097</v>
       </c>
@@ -33091,7 +33091,7 @@
       </c>
       <c r="M83" s="1"/>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="15">
         <v>45097</v>
       </c>
@@ -33128,7 +33128,7 @@
       </c>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="15">
         <v>45097</v>
       </c>
@@ -33165,7 +33165,7 @@
       </c>
       <c r="M85" s="1"/>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="15">
         <v>45097</v>
       </c>
@@ -33202,7 +33202,7 @@
       </c>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="15">
         <v>45098</v>
       </c>
@@ -33239,7 +33239,7 @@
       </c>
       <c r="M87" s="1"/>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="15">
         <v>45098</v>
       </c>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="M88" s="1"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="15">
         <v>45098</v>
       </c>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="M89" s="1"/>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="15">
         <v>45098</v>
       </c>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="15">
         <v>45098</v>
       </c>
@@ -33387,7 +33387,7 @@
       </c>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="15">
         <v>45098</v>
       </c>
@@ -33424,7 +33424,7 @@
       </c>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="15">
         <v>45098</v>
       </c>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="15">
         <v>45098</v>
       </c>
@@ -33498,7 +33498,7 @@
       </c>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="15">
         <v>45098</v>
       </c>
@@ -33535,7 +33535,7 @@
       </c>
       <c r="M95" s="1"/>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="15">
         <v>45098</v>
       </c>
@@ -33572,7 +33572,7 @@
       </c>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="15">
         <v>45098</v>
       </c>
@@ -33609,7 +33609,7 @@
       </c>
       <c r="M97" s="1"/>
     </row>
-    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="15">
         <v>45099</v>
       </c>
@@ -33646,7 +33646,7 @@
       </c>
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="15">
         <v>45099</v>
       </c>
@@ -33683,7 +33683,7 @@
       </c>
       <c r="M99" s="1"/>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="15">
         <v>45099</v>
       </c>
@@ -33720,7 +33720,7 @@
       </c>
       <c r="M100" s="1"/>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="15">
         <v>45099</v>
       </c>
@@ -33757,7 +33757,7 @@
       </c>
       <c r="M101" s="1"/>
     </row>
-    <row r="102" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A102" s="16">
         <v>45189</v>
       </c>
@@ -33792,7 +33792,7 @@
       </c>
       <c r="M102" s="2"/>
     </row>
-    <row r="103" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A103" s="16">
         <v>45189</v>
       </c>
@@ -33827,7 +33827,7 @@
       </c>
       <c r="M103" s="2"/>
     </row>
-    <row r="104" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A104" s="16">
         <v>45189</v>
       </c>
@@ -33862,7 +33862,7 @@
       </c>
       <c r="M104" s="2"/>
     </row>
-    <row r="105" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A105" s="16">
         <v>45189</v>
       </c>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="M105" s="2"/>
     </row>
-    <row r="106" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A106" s="16">
         <v>45189</v>
       </c>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="M106" s="2"/>
     </row>
-    <row r="107" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A107" s="16">
         <v>45189</v>
       </c>
@@ -33967,7 +33967,7 @@
       </c>
       <c r="M107" s="2"/>
     </row>
-    <row r="108" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A108" s="16">
         <v>45189</v>
       </c>
@@ -34002,7 +34002,7 @@
       </c>
       <c r="M108" s="2"/>
     </row>
-    <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A109" s="16">
         <v>45189</v>
       </c>
@@ -34037,7 +34037,7 @@
       </c>
       <c r="M109" s="2"/>
     </row>
-    <row r="110" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A110" s="16">
         <v>45189</v>
       </c>
@@ -34072,7 +34072,7 @@
       </c>
       <c r="M110" s="2"/>
     </row>
-    <row r="111" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A111" s="17">
         <v>45189</v>
       </c>
@@ -34107,7 +34107,7 @@
       </c>
       <c r="M111" s="2"/>
     </row>
-    <row r="112" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A112" s="17">
         <v>45189</v>
       </c>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="M112" s="2"/>
     </row>
-    <row r="113" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A113" s="17">
         <v>45189</v>
       </c>
@@ -34177,7 +34177,7 @@
       </c>
       <c r="M113" s="2"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A114" s="17">
         <v>45189</v>
       </c>
@@ -34212,7 +34212,7 @@
       </c>
       <c r="M114" s="2"/>
     </row>
-    <row r="115" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A115" s="17">
         <v>45189</v>
       </c>
@@ -34247,7 +34247,7 @@
       </c>
       <c r="M115" s="2"/>
     </row>
-    <row r="116" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A116" s="17">
         <v>45189</v>
       </c>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="M116" s="2"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A117" s="17">
         <v>45189</v>
       </c>
@@ -34317,7 +34317,7 @@
       </c>
       <c r="M117" s="2"/>
     </row>
-    <row r="118" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A118" s="16">
         <v>45189</v>
       </c>
@@ -34352,7 +34352,7 @@
       </c>
       <c r="M118" s="2"/>
     </row>
-    <row r="119" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A119" s="16">
         <v>45189</v>
       </c>
@@ -34387,7 +34387,7 @@
       </c>
       <c r="M119" s="2"/>
     </row>
-    <row r="120" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A120" s="16">
         <v>45189</v>
       </c>
@@ -34422,7 +34422,7 @@
       </c>
       <c r="M120" s="2"/>
     </row>
-    <row r="121" spans="1:13" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
       <c r="A121" s="16">
         <v>45189</v>
       </c>
@@ -34457,7 +34457,7 @@
       </c>
       <c r="M121" s="2"/>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="15">
         <v>45342</v>
       </c>
@@ -34496,7 +34496,7 @@
       </c>
       <c r="M122" s="1"/>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="15">
         <v>45342</v>
       </c>
@@ -34531,7 +34531,7 @@
       </c>
       <c r="M123" s="1"/>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="15">
         <v>45342</v>
       </c>
@@ -34570,7 +34570,7 @@
       </c>
       <c r="M124" s="1"/>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="15">
         <v>45342</v>
       </c>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="M125" s="1"/>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="15">
         <v>45342</v>
       </c>
@@ -34644,7 +34644,7 @@
       </c>
       <c r="M126" s="1"/>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="15">
         <v>45342</v>
       </c>
@@ -34679,7 +34679,7 @@
       </c>
       <c r="M127" s="1"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="15">
         <v>45342</v>
       </c>
@@ -34718,7 +34718,7 @@
       </c>
       <c r="M128" s="1"/>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="15">
         <v>45342</v>
       </c>
@@ -34753,7 +34753,7 @@
       </c>
       <c r="M129" s="1"/>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="15">
         <v>45342</v>
       </c>
@@ -34792,7 +34792,7 @@
       </c>
       <c r="M130" s="1"/>
     </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="15">
         <v>45342</v>
       </c>
@@ -34827,7 +34827,7 @@
       </c>
       <c r="M131" s="1"/>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="15">
         <v>45342</v>
       </c>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="M132" s="1"/>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="15">
         <v>45342</v>
       </c>
@@ -34901,7 +34901,7 @@
       </c>
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="15">
         <v>45343</v>
       </c>
@@ -34940,7 +34940,7 @@
       </c>
       <c r="M134" s="1"/>
     </row>
-    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="15">
         <v>45343</v>
       </c>
@@ -34975,7 +34975,7 @@
       </c>
       <c r="M135" s="1"/>
     </row>
-    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="15">
         <v>45343</v>
       </c>
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="15">
         <v>45343</v>
       </c>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="M137" s="1"/>
     </row>
-    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="15">
         <v>45343</v>
       </c>
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M138" s="1"/>
     </row>
-    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="15">
         <v>45343</v>
       </c>
@@ -35119,7 +35119,7 @@
       </c>
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="15">
         <v>45343</v>
       </c>
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M140" s="1"/>
     </row>
-    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="15">
         <v>45343</v>
       </c>
@@ -35189,7 +35189,7 @@
       </c>
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="15">
         <v>45477</v>
       </c>
@@ -35222,7 +35222,7 @@
       <c r="L142" s="1"/>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="15">
         <v>45477</v>
       </c>
@@ -35255,7 +35255,7 @@
       </c>
       <c r="M143" s="1"/>
     </row>
-    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="15">
         <v>45477</v>
       </c>
@@ -35288,7 +35288,7 @@
       </c>
       <c r="M144" s="1"/>
     </row>
-    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="15">
         <v>45477</v>
       </c>
@@ -35321,7 +35321,7 @@
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
     </row>
-    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="15">
         <v>45477</v>
       </c>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="M146" s="1"/>
     </row>
-    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="15">
         <v>45477</v>
       </c>
@@ -35387,7 +35387,7 @@
       </c>
       <c r="M147" s="1"/>
     </row>
-    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="15">
         <v>45477</v>
       </c>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="M148" s="1"/>
     </row>
-    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="15">
         <v>45477</v>
       </c>
@@ -35453,7 +35453,7 @@
       <c r="L149" s="1"/>
       <c r="M149" s="1"/>
     </row>
-    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="15">
         <v>45477</v>
       </c>
@@ -35486,7 +35486,7 @@
       </c>
       <c r="M150" s="1"/>
     </row>
-    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="15">
         <v>45477</v>
       </c>
@@ -35519,7 +35519,7 @@
       </c>
       <c r="M151" s="1"/>
     </row>
-    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="15">
         <v>45477</v>
       </c>
@@ -35552,7 +35552,7 @@
       <c r="L152" s="1"/>
       <c r="M152" s="1"/>
     </row>
-    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="15">
         <v>45477</v>
       </c>
@@ -35585,7 +35585,7 @@
       </c>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="15">
         <v>45477</v>
       </c>
@@ -35618,7 +35618,7 @@
       </c>
       <c r="M154" s="1"/>
     </row>
-    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="15">
         <v>45477</v>
       </c>
@@ -35651,7 +35651,7 @@
       </c>
       <c r="M155" s="1"/>
     </row>
-    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="15">
         <v>45477</v>
       </c>
@@ -35684,7 +35684,7 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
     </row>
-    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="15">
         <v>45477</v>
       </c>
@@ -35717,7 +35717,7 @@
       </c>
       <c r="M157" s="1"/>
     </row>
-    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="15">
         <v>45477</v>
       </c>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="M158" s="1"/>
     </row>
-    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="15">
         <v>45477</v>
       </c>
@@ -35783,7 +35783,7 @@
       <c r="L159" s="1"/>
       <c r="M159" s="1"/>
     </row>
-    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="15">
         <v>45477</v>
       </c>
@@ -35816,7 +35816,7 @@
       </c>
       <c r="M160" s="1"/>
     </row>
-    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="15">
         <v>45477</v>
       </c>
@@ -35849,7 +35849,7 @@
       </c>
       <c r="M161" s="1"/>
     </row>
-    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="15">
         <v>45477</v>
       </c>
@@ -35882,7 +35882,7 @@
       </c>
       <c r="M162" s="1"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="15">
         <v>45477</v>
       </c>
@@ -35917,7 +35917,7 @@
       </c>
       <c r="M163" s="1"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="15">
         <v>45477</v>
       </c>
@@ -35950,7 +35950,7 @@
       </c>
       <c r="M164" s="1"/>
     </row>
-    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="15">
         <v>45477</v>
       </c>
@@ -35983,7 +35983,7 @@
       </c>
       <c r="M165" s="1"/>
     </row>
-    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="15">
         <v>45477</v>
       </c>
@@ -36016,7 +36016,7 @@
       <c r="L166" s="1"/>
       <c r="M166" s="1"/>
     </row>
-    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="15">
         <v>45477</v>
       </c>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="M167" s="1"/>
     </row>
-    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="15">
         <v>45477</v>
       </c>
@@ -36082,7 +36082,7 @@
       </c>
       <c r="M168" s="1"/>
     </row>
-    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="15">
         <v>45477</v>
       </c>
@@ -36115,7 +36115,7 @@
       </c>
       <c r="M169" s="1"/>
     </row>
-    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="15" t="s">
         <v>463</v>
       </c>
@@ -36148,7 +36148,7 @@
       <c r="L170" s="1"/>
       <c r="M170" s="1"/>
     </row>
-    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="15" t="s">
         <v>463</v>
       </c>
@@ -36181,7 +36181,7 @@
       </c>
       <c r="M171" s="1"/>
     </row>
-    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="15" t="s">
         <v>463</v>
       </c>
@@ -36214,7 +36214,7 @@
       </c>
       <c r="M172" s="1"/>
     </row>
-    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="15" t="s">
         <v>463</v>
       </c>
@@ -36247,7 +36247,7 @@
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
     </row>
-    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="15" t="s">
         <v>463</v>
       </c>
@@ -36280,7 +36280,7 @@
       </c>
       <c r="M174" s="1"/>
     </row>
-    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="15" t="s">
         <v>463</v>
       </c>
@@ -36313,7 +36313,7 @@
       </c>
       <c r="M175" s="1"/>
     </row>
-    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="15" t="s">
         <v>463</v>
       </c>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="M176" s="1"/>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="15" t="s">
         <v>463</v>
       </c>
@@ -36379,7 +36379,7 @@
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="15" t="s">
         <v>463</v>
       </c>
@@ -36412,7 +36412,7 @@
       </c>
       <c r="M178" s="1"/>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="15" t="s">
         <v>463</v>
       </c>
@@ -36445,7 +36445,7 @@
       </c>
       <c r="M179" s="1"/>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="15" t="s">
         <v>463</v>
       </c>
@@ -36478,7 +36478,7 @@
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
     </row>
-    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="15" t="s">
         <v>463</v>
       </c>
@@ -36511,7 +36511,7 @@
       </c>
       <c r="M181" s="1"/>
     </row>
-    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="15" t="s">
         <v>463</v>
       </c>
@@ -36544,7 +36544,7 @@
       </c>
       <c r="M182" s="1"/>
     </row>
-    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="15" t="s">
         <v>463</v>
       </c>
@@ -36577,7 +36577,7 @@
       </c>
       <c r="M183" s="1"/>
     </row>
-    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="15" t="s">
         <v>463</v>
       </c>
@@ -36610,7 +36610,7 @@
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
     </row>
-    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="15" t="s">
         <v>463</v>
       </c>
@@ -36643,7 +36643,7 @@
       </c>
       <c r="M185" s="1"/>
     </row>
-    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="15" t="s">
         <v>463</v>
       </c>
@@ -36676,7 +36676,7 @@
       </c>
       <c r="M186" s="1"/>
     </row>
-    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="15" t="s">
         <v>463</v>
       </c>
@@ -36709,7 +36709,7 @@
       <c r="L187" s="1"/>
       <c r="M187" s="1"/>
     </row>
-    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="15" t="s">
         <v>463</v>
       </c>
@@ -36742,7 +36742,7 @@
       </c>
       <c r="M188" s="1"/>
     </row>
-    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="15" t="s">
         <v>463</v>
       </c>
@@ -36775,7 +36775,7 @@
       </c>
       <c r="M189" s="1"/>
     </row>
-    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="15" t="s">
         <v>463</v>
       </c>
@@ -36808,7 +36808,7 @@
       </c>
       <c r="M190" s="1"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="15" t="s">
         <v>463</v>
       </c>
@@ -36841,7 +36841,7 @@
       <c r="L191" s="1"/>
       <c r="M191" s="1"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="15" t="s">
         <v>463</v>
       </c>
@@ -36874,7 +36874,7 @@
       </c>
       <c r="M192" s="1"/>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="15" t="s">
         <v>463</v>
       </c>
@@ -36907,7 +36907,7 @@
       </c>
       <c r="M193" s="1"/>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="15" t="s">
         <v>463</v>
       </c>
@@ -36940,7 +36940,7 @@
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
     </row>
-    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="15" t="s">
         <v>463</v>
       </c>
@@ -36973,7 +36973,7 @@
       </c>
       <c r="M195" s="1"/>
     </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="15" t="s">
         <v>463</v>
       </c>
@@ -37006,7 +37006,7 @@
       </c>
       <c r="M196" s="1"/>
     </row>
-    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="15" t="s">
         <v>463</v>
       </c>
@@ -37039,7 +37039,7 @@
       </c>
       <c r="M197" s="1"/>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="15" t="s">
         <v>520</v>
       </c>
@@ -37072,7 +37072,7 @@
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="15" t="s">
         <v>520</v>
       </c>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="M199" s="1"/>
     </row>
-    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="15" t="s">
         <v>520</v>
       </c>
@@ -37138,7 +37138,7 @@
       </c>
       <c r="M200" s="1"/>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="15" t="s">
         <v>520</v>
       </c>
@@ -37171,7 +37171,7 @@
       <c r="L201" s="1"/>
       <c r="M201" s="1"/>
     </row>
-    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="15" t="s">
         <v>520</v>
       </c>
@@ -37204,7 +37204,7 @@
       </c>
       <c r="M202" s="1"/>
     </row>
-    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="15" t="s">
         <v>520</v>
       </c>
@@ -37237,7 +37237,7 @@
       </c>
       <c r="M203" s="1"/>
     </row>
-    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="15" t="s">
         <v>520</v>
       </c>
@@ -37270,7 +37270,7 @@
       <c r="L204" s="1"/>
       <c r="M204" s="1"/>
     </row>
-    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="15" t="s">
         <v>520</v>
       </c>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="M205" s="1"/>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="15" t="s">
         <v>520</v>
       </c>
@@ -37336,7 +37336,7 @@
       </c>
       <c r="M206" s="1"/>
     </row>
-    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="15" t="s">
         <v>520</v>
       </c>
@@ -37369,7 +37369,7 @@
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="15" t="s">
         <v>520</v>
       </c>
@@ -37402,7 +37402,7 @@
       </c>
       <c r="M208" s="1"/>
     </row>
-    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="15" t="s">
         <v>520</v>
       </c>
@@ -37435,7 +37435,7 @@
       </c>
       <c r="M209" s="1"/>
     </row>
-    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="15" t="s">
         <v>520</v>
       </c>
@@ -37468,7 +37468,7 @@
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
     </row>
-    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="15" t="s">
         <v>520</v>
       </c>
@@ -37499,7 +37499,7 @@
       <c r="L211" s="1"/>
       <c r="M211" s="1"/>
     </row>
-    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="15" t="s">
         <v>520</v>
       </c>
@@ -37532,7 +37532,7 @@
       </c>
       <c r="M212" s="1"/>
     </row>
-    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="15" t="s">
         <v>520</v>
       </c>
@@ -37565,7 +37565,7 @@
       <c r="L213" s="1"/>
       <c r="M213" s="1"/>
     </row>
-    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="15" t="s">
         <v>520</v>
       </c>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="M214" s="1"/>
     </row>
-    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="15" t="s">
         <v>520</v>
       </c>
@@ -37631,7 +37631,7 @@
       </c>
       <c r="M215" s="1"/>
     </row>
-    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="15" t="s">
         <v>520</v>
       </c>
@@ -37664,7 +37664,7 @@
       <c r="L216" s="1"/>
       <c r="M216" s="1"/>
     </row>
-    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="15" t="s">
         <v>520</v>
       </c>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="M217" s="1"/>
     </row>
-    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="15" t="s">
         <v>520</v>
       </c>
@@ -37730,7 +37730,7 @@
       </c>
       <c r="M218" s="1"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="15" t="s">
         <v>520</v>
       </c>
@@ -37763,7 +37763,7 @@
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="15" t="s">
         <v>520</v>
       </c>
@@ -37796,7 +37796,7 @@
       </c>
       <c r="M220" s="1"/>
     </row>
-    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="15" t="s">
         <v>520</v>
       </c>
@@ -37827,7 +37827,7 @@
       </c>
       <c r="M221" s="1"/>
     </row>
-    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="15">
         <v>45824</v>
       </c>
@@ -37860,7 +37860,7 @@
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
     </row>
-    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="15"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -37887,7 +37887,7 @@
       </c>
       <c r="M223" s="1"/>
     </row>
-    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="15"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -37914,7 +37914,7 @@
       </c>
       <c r="M224" s="1"/>
     </row>
-    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="15">
         <v>45824</v>
       </c>
@@ -37947,7 +37947,7 @@
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
     </row>
-    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="15"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="M226" s="1"/>
     </row>
-    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="15"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="M227" s="1"/>
     </row>
-    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="15"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="M228" s="1"/>
     </row>
-    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="15">
         <v>45824</v>
       </c>
@@ -38061,7 +38061,7 @@
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
     </row>
-    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="15"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -38088,7 +38088,7 @@
       </c>
       <c r="M230" s="1"/>
     </row>
-    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="15"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -38115,7 +38115,7 @@
       </c>
       <c r="M231" s="1"/>
     </row>
-    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="15">
         <v>45824</v>
       </c>
@@ -38148,7 +38148,7 @@
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
     </row>
-    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="15"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -38175,7 +38175,7 @@
       </c>
       <c r="M233" s="1"/>
     </row>
-    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="15"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -38202,7 +38202,7 @@
       </c>
       <c r="M234" s="1"/>
     </row>
-    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="15"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="M235" s="1"/>
     </row>
-    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="15">
         <v>45824</v>
       </c>
@@ -38262,7 +38262,7 @@
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
     </row>
-    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="15"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -38289,7 +38289,7 @@
       </c>
       <c r="M237" s="1"/>
     </row>
-    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="15"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -38316,7 +38316,7 @@
       </c>
       <c r="M238" s="1"/>
     </row>
-    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="15">
         <v>45824</v>
       </c>
@@ -38349,7 +38349,7 @@
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
     </row>
-    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="15"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -38376,7 +38376,7 @@
       </c>
       <c r="M240" s="1"/>
     </row>
-    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="15"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -38403,7 +38403,7 @@
       </c>
       <c r="M241" s="1"/>
     </row>
-    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="15"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -38430,7 +38430,7 @@
       </c>
       <c r="M242" s="1"/>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="15">
         <v>45824</v>
       </c>
@@ -38463,7 +38463,7 @@
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="15"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -38490,7 +38490,7 @@
       </c>
       <c r="M244" s="1"/>
     </row>
-    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="15"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -38517,7 +38517,7 @@
       </c>
       <c r="M245" s="1"/>
     </row>
-    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="15">
         <v>45824</v>
       </c>
@@ -38550,7 +38550,7 @@
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="15"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="M247" s="1"/>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="15"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -38604,7 +38604,7 @@
       </c>
       <c r="M248" s="1"/>
     </row>
-    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="15"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -38631,7 +38631,7 @@
       </c>
       <c r="M249" s="1"/>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="15">
         <v>45868</v>
       </c>
@@ -38668,7 +38668,7 @@
       </c>
       <c r="M250" s="1"/>
     </row>
-    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="15">
         <v>45868</v>
       </c>
@@ -38705,7 +38705,7 @@
       </c>
       <c r="M251" s="1"/>
     </row>
-    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="15">
         <v>45868</v>
       </c>
@@ -38742,7 +38742,7 @@
       </c>
       <c r="M252" s="1"/>
     </row>
-    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="15">
         <v>45868</v>
       </c>
@@ -38779,7 +38779,7 @@
       </c>
       <c r="M253" s="1"/>
     </row>
-    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="15">
         <v>45868</v>
       </c>
@@ -38816,7 +38816,7 @@
       </c>
       <c r="M254" s="1"/>
     </row>
-    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="15">
         <v>45868</v>
       </c>
@@ -38853,7 +38853,7 @@
       </c>
       <c r="M255" s="1"/>
     </row>
-    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="15">
         <v>45868</v>
       </c>
@@ -38890,7 +38890,7 @@
       </c>
       <c r="M256" s="1"/>
     </row>
-    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="15">
         <v>45868</v>
       </c>
@@ -38927,7 +38927,7 @@
       </c>
       <c r="M257" s="1"/>
     </row>
-    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="15">
         <v>45868</v>
       </c>
@@ -38964,7 +38964,7 @@
       </c>
       <c r="M258" s="1"/>
     </row>
-    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="15">
         <v>45868</v>
       </c>
@@ -39001,7 +39001,7 @@
       </c>
       <c r="M259" s="1"/>
     </row>
-    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="15">
         <v>45868</v>
       </c>
@@ -39038,7 +39038,7 @@
       </c>
       <c r="M260" s="1"/>
     </row>
-    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="15">
         <v>45868</v>
       </c>
@@ -39075,7 +39075,7 @@
       </c>
       <c r="M261" s="1"/>
     </row>
-    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="15">
         <v>45868</v>
       </c>
@@ -39112,7 +39112,7 @@
       </c>
       <c r="M262" s="1"/>
     </row>
-    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="15">
         <v>45868</v>
       </c>
@@ -39149,7 +39149,7 @@
       </c>
       <c r="M263" s="1"/>
     </row>
-    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="15">
         <v>45868</v>
       </c>
@@ -39186,7 +39186,7 @@
       </c>
       <c r="M264" s="1"/>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="15">
         <v>45868</v>
       </c>
@@ -39223,7 +39223,7 @@
       </c>
       <c r="M265" s="1"/>
     </row>
-    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="15">
         <v>45868</v>
       </c>
@@ -39260,7 +39260,7 @@
       </c>
       <c r="M266" s="1"/>
     </row>
-    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="15">
         <v>45868</v>
       </c>
@@ -39297,7 +39297,7 @@
       </c>
       <c r="M267" s="1"/>
     </row>
-    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="15">
         <v>45868</v>
       </c>
@@ -39334,7 +39334,7 @@
       </c>
       <c r="M268" s="1"/>
     </row>
-    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="15">
         <v>45868</v>
       </c>
@@ -39371,7 +39371,7 @@
       </c>
       <c r="M269" s="1"/>
     </row>
-    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="15">
         <v>45477</v>
       </c>
@@ -39404,7 +39404,7 @@
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
     </row>
-    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="15">
         <v>45477</v>
       </c>
@@ -39437,7 +39437,7 @@
       </c>
       <c r="M271" s="1"/>
     </row>
-    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="15">
         <v>45477</v>
       </c>
@@ -39470,7 +39470,7 @@
       </c>
       <c r="M272" s="1"/>
     </row>
-    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="15">
         <v>45477</v>
       </c>
@@ -39503,7 +39503,7 @@
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
     </row>
-    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="15">
         <v>45477</v>
       </c>
@@ -39536,7 +39536,7 @@
       </c>
       <c r="M274" s="1"/>
     </row>
-    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="15">
         <v>45477</v>
       </c>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="M275" s="1"/>
     </row>
-    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="15">
         <v>45477</v>
       </c>
@@ -39602,7 +39602,7 @@
       </c>
       <c r="M276" s="1"/>
     </row>
-    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="15">
         <v>45477</v>
       </c>
@@ -39635,7 +39635,7 @@
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
     </row>
-    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="15">
         <v>45477</v>
       </c>
@@ -39668,7 +39668,7 @@
       </c>
       <c r="M278" s="1"/>
     </row>
-    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="15">
         <v>45477</v>
       </c>
@@ -39701,7 +39701,7 @@
       </c>
       <c r="M279" s="1"/>
     </row>
-    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="15">
         <v>45477</v>
       </c>
@@ -39734,7 +39734,7 @@
       <c r="L280" s="1"/>
       <c r="M280" s="1"/>
     </row>
-    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="15">
         <v>45477</v>
       </c>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="M281" s="1"/>
     </row>
-    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="15">
         <v>45477</v>
       </c>
@@ -39800,7 +39800,7 @@
       </c>
       <c r="M282" s="1"/>
     </row>
-    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="15">
         <v>45477</v>
       </c>
@@ -39833,7 +39833,7 @@
       </c>
       <c r="M283" s="1"/>
     </row>
-    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="15">
         <v>45477</v>
       </c>
@@ -39866,7 +39866,7 @@
       <c r="L284" s="1"/>
       <c r="M284" s="1"/>
     </row>
-    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="15">
         <v>45477</v>
       </c>
@@ -39899,7 +39899,7 @@
       </c>
       <c r="M285" s="1"/>
     </row>
-    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="15">
         <v>45477</v>
       </c>
@@ -39932,7 +39932,7 @@
       </c>
       <c r="M286" s="1"/>
     </row>
-    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="15">
         <v>45477</v>
       </c>
@@ -39965,7 +39965,7 @@
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
     </row>
-    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="15">
         <v>45477</v>
       </c>
@@ -39998,7 +39998,7 @@
       </c>
       <c r="M288" s="1"/>
     </row>
-    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="15">
         <v>45477</v>
       </c>
@@ -40031,7 +40031,7 @@
       </c>
       <c r="M289" s="1"/>
     </row>
-    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="15">
         <v>45477</v>
       </c>
@@ -40064,7 +40064,7 @@
       </c>
       <c r="M290" s="1"/>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="15">
         <v>45477</v>
       </c>
@@ -40099,7 +40099,7 @@
       </c>
       <c r="M291" s="1"/>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="15">
         <v>45477</v>
       </c>
@@ -40132,7 +40132,7 @@
       </c>
       <c r="M292" s="1"/>
     </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="15">
         <v>45477</v>
       </c>
@@ -40165,7 +40165,7 @@
       </c>
       <c r="M293" s="1"/>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="15">
         <v>45477</v>
       </c>
@@ -40198,7 +40198,7 @@
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
     </row>
-    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="15">
         <v>45477</v>
       </c>
@@ -40231,7 +40231,7 @@
       </c>
       <c r="M295" s="1"/>
     </row>
-    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="15">
         <v>45477</v>
       </c>
@@ -40264,7 +40264,7 @@
       </c>
       <c r="M296" s="1"/>
     </row>
-    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="15">
         <v>45477</v>
       </c>
@@ -40297,7 +40297,7 @@
       </c>
       <c r="M297" s="1"/>
     </row>
-    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="15" t="s">
         <v>463</v>
       </c>
@@ -40330,7 +40330,7 @@
       <c r="L298" s="1"/>
       <c r="M298" s="1"/>
     </row>
-    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="15" t="s">
         <v>463</v>
       </c>
@@ -40363,7 +40363,7 @@
       </c>
       <c r="M299" s="1"/>
     </row>
-    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="15" t="s">
         <v>463</v>
       </c>
@@ -40396,7 +40396,7 @@
       </c>
       <c r="M300" s="1"/>
     </row>
-    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="15" t="s">
         <v>463</v>
       </c>
@@ -40429,7 +40429,7 @@
       <c r="L301" s="1"/>
       <c r="M301" s="1"/>
     </row>
-    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="15" t="s">
         <v>463</v>
       </c>
@@ -40462,7 +40462,7 @@
       </c>
       <c r="M302" s="1"/>
     </row>
-    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="15" t="s">
         <v>463</v>
       </c>
@@ -40495,7 +40495,7 @@
       </c>
       <c r="M303" s="1"/>
     </row>
-    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="15" t="s">
         <v>463</v>
       </c>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="M304" s="1"/>
     </row>
-    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="15" t="s">
         <v>463</v>
       </c>
@@ -40561,7 +40561,7 @@
       <c r="L305" s="1"/>
       <c r="M305" s="1"/>
     </row>
-    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="15" t="s">
         <v>463</v>
       </c>
@@ -40594,7 +40594,7 @@
       </c>
       <c r="M306" s="1"/>
     </row>
-    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="15" t="s">
         <v>463</v>
       </c>
@@ -40627,7 +40627,7 @@
       </c>
       <c r="M307" s="1"/>
     </row>
-    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="15" t="s">
         <v>463</v>
       </c>
@@ -40660,7 +40660,7 @@
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
     </row>
-    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="15" t="s">
         <v>463</v>
       </c>
@@ -40693,7 +40693,7 @@
       </c>
       <c r="M309" s="1"/>
     </row>
-    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="15" t="s">
         <v>463</v>
       </c>
@@ -40726,7 +40726,7 @@
       </c>
       <c r="M310" s="1"/>
     </row>
-    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="15" t="s">
         <v>463</v>
       </c>
@@ -40759,7 +40759,7 @@
       </c>
       <c r="M311" s="1"/>
     </row>
-    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="15" t="s">
         <v>463</v>
       </c>
@@ -40792,7 +40792,7 @@
       <c r="L312" s="1"/>
       <c r="M312" s="1"/>
     </row>
-    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="15" t="s">
         <v>463</v>
       </c>
@@ -40825,7 +40825,7 @@
       </c>
       <c r="M313" s="1"/>
     </row>
-    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="15" t="s">
         <v>463</v>
       </c>
@@ -40858,7 +40858,7 @@
       </c>
       <c r="M314" s="1"/>
     </row>
-    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="15" t="s">
         <v>463</v>
       </c>
@@ -40891,7 +40891,7 @@
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
     </row>
-    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="15" t="s">
         <v>463</v>
       </c>
@@ -40924,7 +40924,7 @@
       </c>
       <c r="M316" s="1"/>
     </row>
-    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="15" t="s">
         <v>463</v>
       </c>
@@ -40957,7 +40957,7 @@
       </c>
       <c r="M317" s="1"/>
     </row>
-    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="15" t="s">
         <v>463</v>
       </c>
@@ -40990,7 +40990,7 @@
       </c>
       <c r="M318" s="1"/>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="15" t="s">
         <v>463</v>
       </c>
@@ -41023,7 +41023,7 @@
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="15" t="s">
         <v>463</v>
       </c>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="M320" s="1"/>
     </row>
-    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="15" t="s">
         <v>463</v>
       </c>
@@ -41089,7 +41089,7 @@
       </c>
       <c r="M321" s="1"/>
     </row>
-    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="15" t="s">
         <v>463</v>
       </c>
@@ -41122,7 +41122,7 @@
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
     </row>
-    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="15" t="s">
         <v>463</v>
       </c>
@@ -41155,7 +41155,7 @@
       </c>
       <c r="M323" s="1"/>
     </row>
-    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="15" t="s">
         <v>463</v>
       </c>
@@ -41188,7 +41188,7 @@
       </c>
       <c r="M324" s="1"/>
     </row>
-    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="15" t="s">
         <v>463</v>
       </c>
@@ -41221,7 +41221,7 @@
       </c>
       <c r="M325" s="1"/>
     </row>
-    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="15" t="s">
         <v>520</v>
       </c>
@@ -41254,7 +41254,7 @@
       <c r="L326" s="1"/>
       <c r="M326" s="1"/>
     </row>
-    <row r="327" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="15" t="s">
         <v>520</v>
       </c>
@@ -41287,7 +41287,7 @@
       </c>
       <c r="M327" s="1"/>
     </row>
-    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="15" t="s">
         <v>520</v>
       </c>
@@ -41320,7 +41320,7 @@
       </c>
       <c r="M328" s="1"/>
     </row>
-    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="15" t="s">
         <v>520</v>
       </c>
@@ -41353,7 +41353,7 @@
       <c r="L329" s="1"/>
       <c r="M329" s="1"/>
     </row>
-    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="15" t="s">
         <v>520</v>
       </c>
@@ -41386,7 +41386,7 @@
       </c>
       <c r="M330" s="1"/>
     </row>
-    <row r="331" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="15" t="s">
         <v>520</v>
       </c>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="M331" s="1"/>
     </row>
-    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="15" t="s">
         <v>520</v>
       </c>
@@ -41452,7 +41452,7 @@
       <c r="L332" s="1"/>
       <c r="M332" s="1"/>
     </row>
-    <row r="333" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="15" t="s">
         <v>520</v>
       </c>
@@ -41485,7 +41485,7 @@
       </c>
       <c r="M333" s="1"/>
     </row>
-    <row r="334" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="15" t="s">
         <v>520</v>
       </c>
@@ -41518,7 +41518,7 @@
       </c>
       <c r="M334" s="1"/>
     </row>
-    <row r="335" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="15" t="s">
         <v>520</v>
       </c>
@@ -41551,7 +41551,7 @@
       <c r="L335" s="1"/>
       <c r="M335" s="1"/>
     </row>
-    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="15" t="s">
         <v>520</v>
       </c>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="M336" s="1"/>
     </row>
-    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="15" t="s">
         <v>520</v>
       </c>
@@ -41617,7 +41617,7 @@
       </c>
       <c r="M337" s="1"/>
     </row>
-    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="15" t="s">
         <v>520</v>
       </c>
@@ -41650,7 +41650,7 @@
       <c r="L338" s="1"/>
       <c r="M338" s="1"/>
     </row>
-    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="15" t="s">
         <v>520</v>
       </c>
@@ -41681,7 +41681,7 @@
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
     </row>
-    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="15" t="s">
         <v>520</v>
       </c>
@@ -41714,7 +41714,7 @@
       </c>
       <c r="M340" s="1"/>
     </row>
-    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="15" t="s">
         <v>520</v>
       </c>
@@ -41747,7 +41747,7 @@
       <c r="L341" s="1"/>
       <c r="M341" s="1"/>
     </row>
-    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="15" t="s">
         <v>520</v>
       </c>
@@ -41780,7 +41780,7 @@
       </c>
       <c r="M342" s="1"/>
     </row>
-    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="15" t="s">
         <v>520</v>
       </c>
@@ -41813,7 +41813,7 @@
       </c>
       <c r="M343" s="1"/>
     </row>
-    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="15" t="s">
         <v>520</v>
       </c>
@@ -41846,7 +41846,7 @@
       <c r="L344" s="1"/>
       <c r="M344" s="1"/>
     </row>
-    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="15" t="s">
         <v>520</v>
       </c>
@@ -41879,7 +41879,7 @@
       </c>
       <c r="M345" s="1"/>
     </row>
-    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="15" t="s">
         <v>520</v>
       </c>
@@ -41912,7 +41912,7 @@
       </c>
       <c r="M346" s="1"/>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="15" t="s">
         <v>520</v>
       </c>
@@ -41945,7 +41945,7 @@
       <c r="L347" s="1"/>
       <c r="M347" s="1"/>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="15" t="s">
         <v>520</v>
       </c>
@@ -41978,7 +41978,7 @@
       </c>
       <c r="M348" s="1"/>
     </row>
-    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="15" t="s">
         <v>520</v>
       </c>
@@ -42009,7 +42009,7 @@
       </c>
       <c r="M349" s="1"/>
     </row>
-    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="15">
         <v>45741</v>
       </c>
@@ -42042,7 +42042,7 @@
       <c r="L350" s="1"/>
       <c r="M350" s="1"/>
     </row>
-    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="15"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -42069,7 +42069,7 @@
       </c>
       <c r="M351" s="1"/>
     </row>
-    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="15"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -42096,7 +42096,7 @@
       </c>
       <c r="M352" s="1"/>
     </row>
-    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="15">
         <v>45741</v>
       </c>
@@ -42129,7 +42129,7 @@
       <c r="L353" s="1"/>
       <c r="M353" s="1"/>
     </row>
-    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="15"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -42156,7 +42156,7 @@
       </c>
       <c r="M354" s="1"/>
     </row>
-    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="15"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -42183,7 +42183,7 @@
       </c>
       <c r="M355" s="1"/>
     </row>
-    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="15">
         <v>45741</v>
       </c>
@@ -42216,7 +42216,7 @@
       <c r="L356" s="1"/>
       <c r="M356" s="1"/>
     </row>
-    <row r="357" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="15"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -42243,7 +42243,7 @@
       </c>
       <c r="M357" s="1"/>
     </row>
-    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="15"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="M358" s="1"/>
     </row>
-    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="15">
         <v>45741</v>
       </c>
@@ -42303,7 +42303,7 @@
       <c r="L359" s="1"/>
       <c r="M359" s="1"/>
     </row>
-    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="15"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -42330,7 +42330,7 @@
       </c>
       <c r="M360" s="1"/>
     </row>
-    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="15"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -42357,7 +42357,7 @@
       </c>
       <c r="M361" s="1"/>
     </row>
-    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="15">
         <v>45741</v>
       </c>
@@ -42390,7 +42390,7 @@
       <c r="L362" s="1"/>
       <c r="M362" s="1"/>
     </row>
-    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="15"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -42417,7 +42417,7 @@
       </c>
       <c r="M363" s="1"/>
     </row>
-    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="15"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -42444,7 +42444,7 @@
       </c>
       <c r="M364" s="1"/>
     </row>
-    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="15">
         <v>45741</v>
       </c>
@@ -42477,7 +42477,7 @@
       <c r="L365" s="1"/>
       <c r="M365" s="1"/>
     </row>
-    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="15"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -42504,7 +42504,7 @@
       </c>
       <c r="M366" s="1"/>
     </row>
-    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="15"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -42531,7 +42531,7 @@
       </c>
       <c r="M367" s="1"/>
     </row>
-    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="15">
         <v>45741</v>
       </c>
@@ -42564,7 +42564,7 @@
       <c r="L368" s="1"/>
       <c r="M368" s="1"/>
     </row>
-    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="15"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -42591,7 +42591,7 @@
       </c>
       <c r="M369" s="1"/>
     </row>
-    <row r="370" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="15"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -42618,7 +42618,7 @@
       </c>
       <c r="M370" s="1"/>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="15">
         <v>45741</v>
       </c>
@@ -42651,7 +42651,7 @@
       <c r="L371" s="1"/>
       <c r="M371" s="1"/>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="15"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -42678,7 +42678,7 @@
       </c>
       <c r="M372" s="1"/>
     </row>
-    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="15"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -42705,7 +42705,7 @@
       </c>
       <c r="M373" s="1"/>
     </row>
-    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="15">
         <v>45824</v>
       </c>
@@ -42738,7 +42738,7 @@
       <c r="L374" s="1"/>
       <c r="M374" s="1"/>
     </row>
-    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="15">
         <v>45824</v>
       </c>
@@ -42771,7 +42771,7 @@
       </c>
       <c r="M375" s="1"/>
     </row>
-    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="15">
         <v>45824</v>
       </c>
@@ -42804,7 +42804,7 @@
       </c>
       <c r="M376" s="1"/>
     </row>
-    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="15">
         <v>45824</v>
       </c>
@@ -42837,7 +42837,7 @@
       <c r="L377" s="1"/>
       <c r="M377" s="1"/>
     </row>
-    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="15">
         <v>45824</v>
       </c>
@@ -42870,7 +42870,7 @@
       </c>
       <c r="M378" s="1"/>
     </row>
-    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="15">
         <v>45824</v>
       </c>
@@ -42903,7 +42903,7 @@
       </c>
       <c r="M379" s="1"/>
     </row>
-    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="15">
         <v>45824</v>
       </c>
@@ -42936,7 +42936,7 @@
       </c>
       <c r="M380" s="1"/>
     </row>
-    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="15">
         <v>45824</v>
       </c>
@@ -42969,7 +42969,7 @@
       <c r="L381" s="1"/>
       <c r="M381" s="1"/>
     </row>
-    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="15">
         <v>45824</v>
       </c>
@@ -43002,7 +43002,7 @@
       </c>
       <c r="M382" s="1"/>
     </row>
-    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="15">
         <v>45824</v>
       </c>
@@ -43035,7 +43035,7 @@
       </c>
       <c r="M383" s="1"/>
     </row>
-    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="15">
         <v>45824</v>
       </c>
@@ -43068,7 +43068,7 @@
       <c r="L384" s="1"/>
       <c r="M384" s="1"/>
     </row>
-    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="15">
         <v>45824</v>
       </c>
@@ -43101,7 +43101,7 @@
       </c>
       <c r="M385" s="1"/>
     </row>
-    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="15">
         <v>45824</v>
       </c>
@@ -43134,7 +43134,7 @@
       </c>
       <c r="M386" s="1"/>
     </row>
-    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="15">
         <v>45824</v>
       </c>
@@ -43167,7 +43167,7 @@
       </c>
       <c r="M387" s="1"/>
     </row>
-    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="15">
         <v>45824</v>
       </c>
@@ -43200,7 +43200,7 @@
       <c r="L388" s="1"/>
       <c r="M388" s="1"/>
     </row>
-    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="15">
         <v>45824</v>
       </c>
@@ -43233,7 +43233,7 @@
       </c>
       <c r="M389" s="1"/>
     </row>
-    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="15">
         <v>45824</v>
       </c>
@@ -43266,7 +43266,7 @@
       </c>
       <c r="M390" s="1"/>
     </row>
-    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="15">
         <v>45824</v>
       </c>
@@ -43299,7 +43299,7 @@
       <c r="L391" s="1"/>
       <c r="M391" s="1"/>
     </row>
-    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="15">
         <v>45824</v>
       </c>
@@ -43332,7 +43332,7 @@
       </c>
       <c r="M392" s="1"/>
     </row>
-    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="15">
         <v>45824</v>
       </c>
@@ -43365,7 +43365,7 @@
       </c>
       <c r="M393" s="1"/>
     </row>
-    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="15">
         <v>45824</v>
       </c>
@@ -43398,7 +43398,7 @@
       </c>
       <c r="M394" s="1"/>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="15">
         <v>45824</v>
       </c>
@@ -43431,7 +43431,7 @@
       <c r="L395" s="1"/>
       <c r="M395" s="1"/>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="15">
         <v>45824</v>
       </c>
@@ -43464,7 +43464,7 @@
       </c>
       <c r="M396" s="1"/>
     </row>
-    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="15">
         <v>45824</v>
       </c>
@@ -43497,7 +43497,7 @@
       </c>
       <c r="M397" s="1"/>
     </row>
-    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="15">
         <v>45824</v>
       </c>
@@ -43530,7 +43530,7 @@
       <c r="L398" s="1"/>
       <c r="M398" s="1"/>
     </row>
-    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="15">
         <v>45824</v>
       </c>
@@ -43563,7 +43563,7 @@
       </c>
       <c r="M399" s="1"/>
     </row>
-    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="15">
         <v>45824</v>
       </c>
@@ -43596,7 +43596,7 @@
       </c>
       <c r="M400" s="1"/>
     </row>
-    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="15">
         <v>45824</v>
       </c>
@@ -43629,7 +43629,7 @@
       </c>
       <c r="M401" s="1"/>
     </row>
-    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="15">
         <v>45868</v>
       </c>
@@ -43662,7 +43662,7 @@
       </c>
       <c r="M402" s="1"/>
     </row>
-    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="15">
         <v>45868</v>
       </c>
@@ -43695,7 +43695,7 @@
       </c>
       <c r="M403" s="1"/>
     </row>
-    <row r="404" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="15">
         <v>45868</v>
       </c>
@@ -43728,7 +43728,7 @@
       </c>
       <c r="M404" s="1"/>
     </row>
-    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="15">
         <v>45868</v>
       </c>
@@ -43761,7 +43761,7 @@
       </c>
       <c r="M405" s="1"/>
     </row>
-    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="15">
         <v>45868</v>
       </c>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="M406" s="1"/>
     </row>
-    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="15">
         <v>45868</v>
       </c>
@@ -43827,7 +43827,7 @@
       </c>
       <c r="M407" s="1"/>
     </row>
-    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="15">
         <v>45868</v>
       </c>
@@ -43860,7 +43860,7 @@
       </c>
       <c r="M408" s="1"/>
     </row>
-    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="15">
         <v>45868</v>
       </c>
@@ -43893,7 +43893,7 @@
       </c>
       <c r="M409" s="1"/>
     </row>
-    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="15">
         <v>45868</v>
       </c>
@@ -43926,7 +43926,7 @@
       </c>
       <c r="M410" s="1"/>
     </row>
-    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="15">
         <v>45868</v>
       </c>
@@ -43959,7 +43959,7 @@
       </c>
       <c r="M411" s="1"/>
     </row>
-    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" s="15">
         <v>45868</v>
       </c>
@@ -43992,7 +43992,7 @@
       </c>
       <c r="M412" s="1"/>
     </row>
-    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="15">
         <v>45868</v>
       </c>
@@ -44025,7 +44025,7 @@
       </c>
       <c r="M413" s="1"/>
     </row>
-    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" s="15">
         <v>45868</v>
       </c>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="M414" s="1"/>
     </row>
-    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" s="15">
         <v>45868</v>
       </c>
@@ -44091,7 +44091,7 @@
       </c>
       <c r="M415" s="1"/>
     </row>
-    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" s="15">
         <v>45868</v>
       </c>
@@ -44124,7 +44124,7 @@
       </c>
       <c r="M416" s="1"/>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="15">
         <v>45868</v>
       </c>
@@ -44157,7 +44157,7 @@
       </c>
       <c r="M417" s="1"/>
     </row>
-    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" s="15">
         <v>45868</v>
       </c>
@@ -44190,7 +44190,7 @@
       </c>
       <c r="M418" s="1"/>
     </row>
-    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" s="15">
         <v>45868</v>
       </c>
@@ -44223,7 +44223,7 @@
       </c>
       <c r="M419" s="1"/>
     </row>
-    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" s="15">
         <v>45868</v>
       </c>
@@ -44256,7 +44256,7 @@
       </c>
       <c r="M420" s="1"/>
     </row>
-    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" s="15">
         <v>45868</v>
       </c>
@@ -44289,7 +44289,7 @@
       </c>
       <c r="M421" s="1"/>
     </row>
-    <row r="422" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" s="15"/>
       <c r="B422" s="1" t="s">
         <v>176</v>
@@ -44320,7 +44320,7 @@
       <c r="L422" s="1"/>
       <c r="M422" s="1"/>
     </row>
-    <row r="423" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" s="15"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="M423" s="1"/>
     </row>
-    <row r="424" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" s="15"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="M424" s="1"/>
     </row>
-    <row r="425" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" s="15"/>
       <c r="B425" s="1" t="s">
         <v>507</v>
@@ -44405,7 +44405,7 @@
       <c r="L425" s="1"/>
       <c r="M425" s="1"/>
     </row>
-    <row r="426" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" s="15"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -44432,7 +44432,7 @@
       </c>
       <c r="M426" s="1"/>
     </row>
-    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" s="15"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -44459,7 +44459,7 @@
       </c>
       <c r="M427" s="1"/>
     </row>
-    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" s="15"/>
       <c r="B428" s="1" t="s">
         <v>580</v>
@@ -44490,7 +44490,7 @@
       <c r="L428" s="1"/>
       <c r="M428" s="1"/>
     </row>
-    <row r="429" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" s="15"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -44517,7 +44517,7 @@
       </c>
       <c r="M429" s="1"/>
     </row>
-    <row r="430" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" s="15"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -44544,7 +44544,7 @@
       </c>
       <c r="M430" s="1"/>
     </row>
-    <row r="431" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" s="15"/>
       <c r="B431" s="1" t="s">
         <v>705</v>
@@ -44575,7 +44575,7 @@
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
     </row>
-    <row r="432" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" s="15"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -44602,7 +44602,7 @@
       </c>
       <c r="M432" s="1"/>
     </row>
-    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" s="15"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -44629,7 +44629,7 @@
       </c>
       <c r="M433" s="1"/>
     </row>
-    <row r="434" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" s="15"/>
       <c r="B434" s="1" t="s">
         <v>711</v>
@@ -44662,7 +44662,7 @@
       <c r="L434" s="1"/>
       <c r="M434" s="1"/>
     </row>
-    <row r="435" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" s="15"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -44687,7 +44687,7 @@
       <c r="L435" s="1"/>
       <c r="M435" s="1"/>
     </row>
-    <row r="436" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" s="15"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -44712,7 +44712,7 @@
       <c r="L436" s="1"/>
       <c r="M436" s="1"/>
     </row>
-    <row r="437" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" s="15"/>
       <c r="B437" s="1" t="s">
         <v>715</v>
@@ -44743,7 +44743,7 @@
       <c r="L437" s="1"/>
       <c r="M437" s="1"/>
     </row>
-    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" s="15"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -44770,7 +44770,7 @@
       </c>
       <c r="M438" s="1"/>
     </row>
-    <row r="439" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" s="15"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -44797,7 +44797,7 @@
       </c>
       <c r="M439" s="1"/>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" s="15"/>
       <c r="B440" s="1" t="s">
         <v>672</v>
@@ -44828,7 +44828,7 @@
       <c r="L440" s="1"/>
       <c r="M440" s="1"/>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" s="15"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -44855,7 +44855,7 @@
       </c>
       <c r="M441" s="1"/>
     </row>
-    <row r="442" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" s="15"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -44880,7 +44880,7 @@
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
     </row>
-    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" s="15"/>
       <c r="B443" s="1" t="s">
         <v>723</v>
@@ -44911,7 +44911,7 @@
       <c r="L443" s="1"/>
       <c r="M443" s="1"/>
     </row>
-    <row r="444" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" s="15"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -44938,7 +44938,7 @@
       </c>
       <c r="M444" s="1"/>
     </row>
-    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" s="15"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -44980,18 +44980,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D5138A-5DBE-4177-A555-C21D1084B689}">
   <dimension ref="A1:T15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="6" max="6" width="26.140625" customWidth="1"/>
+    <col min="6" max="6" width="26.15625" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="13" width="16.140625" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.578125" customWidth="1"/>
+    <col min="11" max="13" width="16.15625" customWidth="1"/>
+    <col min="14" max="14" width="18.41796875" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -45053,7 +45053,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="18">
         <v>44629</v>
       </c>
@@ -45117,7 +45117,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="18">
         <v>45097</v>
       </c>
@@ -45179,7 +45179,7 @@
       </c>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="18">
         <v>45098</v>
       </c>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="18">
         <v>45342</v>
       </c>
@@ -45305,7 +45305,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="18">
         <v>45477</v>
       </c>
@@ -45363,7 +45363,7 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="18">
         <v>45477</v>
       </c>
@@ -45420,7 +45420,7 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="18">
         <v>45595</v>
       </c>
@@ -45478,7 +45478,7 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="18">
         <v>45595</v>
       </c>
@@ -45535,7 +45535,7 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="18">
         <v>45685</v>
       </c>
@@ -45592,7 +45592,7 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="18">
         <v>45685</v>
       </c>
@@ -45649,7 +45649,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="18">
         <v>45741</v>
       </c>
@@ -45707,7 +45707,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="18">
         <v>45824</v>
       </c>
@@ -45764,7 +45764,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="18">
         <v>45824</v>
       </c>
@@ -45821,7 +45821,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="18"/>
       <c r="B15" s="1" t="s">
         <v>580</v>
@@ -45888,19 +45888,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650E58C5-FA0B-47AA-B1D0-06CBDDB83513}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="6" max="6" width="26.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.15625" customWidth="1"/>
+    <col min="7" max="7" width="14.68359375" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="13" width="16.140625" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.578125" customWidth="1"/>
+    <col min="11" max="13" width="16.15625" customWidth="1"/>
+    <col min="14" max="14" width="18.41796875" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -45962,7 +45962,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15">
         <v>44600</v>
       </c>
@@ -46026,7 +46026,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="15">
         <v>44600</v>
       </c>
@@ -46086,7 +46086,7 @@
       </c>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="15">
         <v>44622</v>
       </c>
@@ -46148,7 +46148,7 @@
       </c>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15">
         <v>44622</v>
       </c>
@@ -46212,7 +46212,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="15">
         <v>44629</v>
       </c>
@@ -46270,7 +46270,7 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15">
         <v>44873</v>
       </c>
@@ -46327,7 +46327,7 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15">
         <v>44873</v>
       </c>
@@ -46385,7 +46385,7 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="15">
         <v>45097</v>
       </c>
@@ -46442,7 +46442,7 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15">
         <v>45098</v>
       </c>
@@ -46499,7 +46499,7 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A11" s="16">
         <v>45189</v>
       </c>
@@ -46556,7 +46556,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A12" s="17">
         <v>45189</v>
       </c>
@@ -46614,7 +46614,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="15">
         <v>45342</v>
       </c>
@@ -46671,7 +46671,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="15">
         <v>45342</v>
       </c>
@@ -46726,7 +46726,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="15">
         <v>45477</v>
       </c>
@@ -46783,7 +46783,7 @@
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="15">
         <v>45477</v>
       </c>
@@ -46804,7 +46804,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="15">
         <v>45477</v>
       </c>
@@ -46825,7 +46825,7 @@
       </c>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="15" t="s">
         <v>463</v>
       </c>
@@ -46848,7 +46848,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="15" t="s">
         <v>463</v>
       </c>
@@ -46869,7 +46869,7 @@
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="15" t="s">
         <v>463</v>
       </c>
@@ -46890,7 +46890,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="15" t="s">
         <v>520</v>
       </c>
@@ -46913,7 +46913,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="15" t="s">
         <v>520</v>
       </c>
@@ -46934,7 +46934,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="15" t="s">
         <v>520</v>
       </c>
@@ -46955,7 +46955,7 @@
       </c>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="15">
         <v>45824</v>
       </c>
@@ -46978,7 +46978,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="15"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -46993,7 +46993,7 @@
       </c>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="15"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -47008,7 +47008,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="15">
         <v>45868</v>
       </c>
@@ -47031,7 +47031,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="15">
         <v>45868</v>
       </c>
@@ -47054,7 +47054,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="15">
         <v>45477</v>
       </c>
@@ -47077,7 +47077,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="15">
         <v>45477</v>
       </c>
@@ -47098,7 +47098,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="15">
         <v>45477</v>
       </c>
@@ -47119,7 +47119,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="15" t="s">
         <v>463</v>
       </c>
@@ -47142,7 +47142,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="15" t="s">
         <v>463</v>
       </c>
@@ -47163,7 +47163,7 @@
       </c>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="15" t="s">
         <v>463</v>
       </c>
@@ -47184,7 +47184,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="15" t="s">
         <v>520</v>
       </c>
@@ -47207,7 +47207,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="15" t="s">
         <v>520</v>
       </c>
@@ -47228,7 +47228,7 @@
       </c>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="15" t="s">
         <v>520</v>
       </c>
@@ -47249,7 +47249,7 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="15">
         <v>45741</v>
       </c>
@@ -47272,7 +47272,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="15"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -47287,7 +47287,7 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="15"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -47302,7 +47302,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="15">
         <v>45824</v>
       </c>
@@ -47325,7 +47325,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="15">
         <v>45824</v>
       </c>
@@ -47346,7 +47346,7 @@
       </c>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="15">
         <v>45824</v>
       </c>
@@ -47367,7 +47367,7 @@
       </c>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="15">
         <v>45868</v>
       </c>
@@ -47388,7 +47388,7 @@
       </c>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="15">
         <v>45868</v>
       </c>
@@ -47409,7 +47409,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="15"/>
       <c r="B46" s="1" t="s">
         <v>507</v>
@@ -47430,7 +47430,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="15"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -47445,7 +47445,7 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="15"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -47469,13 +47469,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FBE892-1990-4771-9A96-311AA3B90DE2}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.578125" customWidth="1"/>
+    <col min="6" max="7" width="8.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -47501,7 +47501,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="13">
         <v>45854</v>
       </c>
@@ -47527,7 +47527,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="13">
         <v>45854</v>
       </c>
@@ -47553,7 +47553,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="13">
         <v>45854</v>
       </c>
@@ -47579,7 +47579,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="13">
         <v>45854</v>
       </c>
@@ -47605,7 +47605,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="13">
         <v>45854</v>
       </c>
@@ -47631,7 +47631,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="13">
         <v>45854</v>
       </c>
@@ -47657,7 +47657,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="13">
         <v>45854</v>
       </c>
@@ -47683,7 +47683,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13">
         <v>45854</v>
       </c>
@@ -47709,7 +47709,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="13">
         <v>45862</v>
       </c>
@@ -47735,7 +47735,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="13">
         <v>45862</v>
       </c>
@@ -47761,7 +47761,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="13">
         <v>45862</v>
       </c>
@@ -47787,7 +47787,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="13">
         <v>45862</v>
       </c>
@@ -47813,7 +47813,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="13">
         <v>45862</v>
       </c>
@@ -47839,7 +47839,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="13">
         <v>45862</v>
       </c>
@@ -47865,7 +47865,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="13">
         <v>45862</v>
       </c>
@@ -47891,7 +47891,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="13">
         <v>45862</v>
       </c>
